--- a/analysis/appliances_purchaseprobability_upd.xlsx
+++ b/analysis/appliances_purchaseprobability_upd.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6330"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12550" windowHeight="2550"/>
   </bookViews>
   <sheets>
     <sheet name="Appliances" sheetId="4" r:id="rId1"/>
@@ -160,7 +160,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2392" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2928" uniqueCount="508">
   <si>
     <t>coder</t>
   </si>
@@ -694,9 +694,6 @@
     <t>Other uncategorised dependent variable</t>
   </si>
   <si>
-    <t>del Mar Sol,  Escapa &amp; Galarraga</t>
-  </si>
-  <si>
     <t>Effectiveness of monetary information in promoting the purchase of energy-efficient appliances: Evidence from a field experiment in Spain</t>
   </si>
   <si>
@@ -1677,6 +1674,96 @@
   </si>
   <si>
     <t>counterfactual</t>
+  </si>
+  <si>
+    <t>del Mar Sola,  Escapa &amp; Galarraga</t>
+  </si>
+  <si>
+    <t>70–400 CNY for refrigerators, 100–400 CNY for televisions, 70–260 CNY for washing machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">probability of choosing an MEE [most energy-efficient] refrigerator </t>
+  </si>
+  <si>
+    <t>Effect on choosing a highly energy efficient refrigerator (MEE)</t>
+  </si>
+  <si>
+    <t>Eco-product subsidy dummy</t>
+  </si>
+  <si>
+    <t>Endogenous treatment. Participants had to actively use the subsidy programm</t>
+  </si>
+  <si>
+    <t>mixed multinomial logit model</t>
+  </si>
+  <si>
+    <t>1995-2014</t>
+  </si>
+  <si>
+    <t>Similar to many countries, China has introduced a variety of incentives to promote the use of energy-efficient appliances. The Chinese government introduced the energy-efficiency labeling program in 2005, and three types of subsidies (i.e., the countryside subsidy, trade-in subsidy, and eco-product subsidy programs) were implemented from 2007 to 2013. In this study, we examine households’ selection of refrigerator energy efficiency and apply a mixed logit model to micro-level data from the Chinese General Social Survey to evaluate the impact of these policies. The analysis demonstrates that the energy-efficiency labeling program as well as the three subsidy programs promoted households’ choice of energy-efficient refrigerators; however, the effects of the various subsidy programs differed. These results suggest that the countryside subsidy has a similar effect as the eco-product subsidy in terms of promoting the purchase of highly energy-efficient refrigerators, although the countryside subsidy’s main objective was to promote appliances being disseminated in rural areas. The trade-in subsidy was less effective in promoting the sale of energy-efficient refrigerators. These findings provide implications for designing future incentive and subsidy policies, particularly for developing countries.</t>
+  </si>
+  <si>
+    <t>Impact of incentives to purchase energy-efficient products: evidence from Chinese households based on a mixed logit model</t>
+  </si>
+  <si>
+    <t>Wang</t>
+  </si>
+  <si>
+    <t>0,10</t>
+  </si>
+  <si>
+    <t>Trade-in subsidy</t>
+  </si>
+  <si>
+    <t>0,13</t>
+  </si>
+  <si>
+    <t>Countryside subsidy</t>
+  </si>
+  <si>
+    <t>Energy-efficiency label (during the 2010–2014 period)</t>
+  </si>
+  <si>
+    <t>Not clear whether the effect is actually due to the label or whether it is due to time trends</t>
+  </si>
+  <si>
+    <t>Energy-efficiency label (implemented during the years 2005–2009)</t>
+  </si>
+  <si>
+    <t>preferences for the energy labelling of refrigerator attributes</t>
+  </si>
+  <si>
+    <t>different specifications of the label</t>
+  </si>
+  <si>
+    <t>Energy label is a widely used policy instrument to increase consumer awareness of energy-efficient home appliances. It helps consumers make better
+informed purchasing decision intending to save on the electricity bill. The increase in energy efficiency for a household can generate significant energy
+savings and emissions reduction which can reduce environmental impact. The energy label targets to fight climate change, protect the environment
+and is significant to support Sustainable Development Goals (SDGs). This study presents the results of a discrete choice experiment (DCE) on the
+East Coast, Malaysia to investigate the consumer preferences for energy label in the purchasing decision of a refrigerator. Multinomial logit (MNL)
+and mixed logit (ML) models are specified to measure the attributes that consumers assess when choosing refrigerators. This study focuses on four
+attributes, namely energy star, energy consumption, energy saving and refrigerator price. Findings show that consumers have responded positively
+to the labels, in which about 88.11% of respondents are willing to pay to get better quality appliances that promote a safe environment while 11.89%
+of respondents are not willing to pay. The findings are useful in improving the effectiveness of existing energy efficiency and labelling programs to
+accelerate the adoption of energy-efficient technology in Malaysia. Hence, the implementation of energy label promotes energy-efficient appliances,
+which is in line with SDG Goal 7: Ensuring access to affordable, reliable, sustainable, and modern energy for all.</t>
+  </si>
+  <si>
+    <t>Consumer Preference for Energy Label in the Purchase Decision
+of Refrigerator: A Discrete Choice Experiment Approach in the
+East Coast, Malaysia</t>
+  </si>
+  <si>
+    <t>Razali, Kamaludin, Azlina</t>
+  </si>
+  <si>
+    <t>star: 5</t>
+  </si>
+  <si>
+    <t>star: 4</t>
+  </si>
+  <si>
+    <t>star: 3</t>
   </si>
 </sst>
 </file>
@@ -1698,7 +1785,7 @@
     <numFmt numFmtId="175" formatCode="0.000000"/>
     <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1832,6 +1919,12 @@
     <font>
       <b/>
       <sz val="10"/>
+      <name val="Calibri Light"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri Light"/>
       <scheme val="major"/>
     </font>
@@ -2046,7 +2139,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2176,6 +2269,7 @@
     <xf numFmtId="10" fontId="15" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="170" fontId="15" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="15" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Link" xfId="2" builtinId="8"/>
@@ -2472,7 +2566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CK343"/>
+  <dimension ref="A1:CL343"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.58203125" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="51" width="10.58203125" style="1"/>
@@ -2490,7 +2584,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1</v>
@@ -7839,16 +7933,16 @@
         <v>513</v>
       </c>
       <c r="E22" s="72" t="s">
-        <v>159</v>
+        <v>482</v>
       </c>
       <c r="F22" s="72">
         <v>2023</v>
       </c>
       <c r="G22" s="72" t="s">
+        <v>159</v>
+      </c>
+      <c r="H22" s="72" t="s">
         <v>160</v>
-      </c>
-      <c r="H22" s="72" t="s">
-        <v>161</v>
       </c>
       <c r="I22" s="72">
         <v>2</v>
@@ -7857,13 +7951,13 @@
         <v>2018</v>
       </c>
       <c r="M22" s="72" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N22" s="72" t="s">
         <v>102</v>
       </c>
       <c r="O22" s="72" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P22" s="72" t="s">
         <v>87</v>
@@ -7890,70 +7984,70 @@
         <v>95</v>
       </c>
       <c r="X22" s="72" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y22" s="72">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="72">
+        <v>1</v>
+      </c>
+      <c r="AA22" s="72">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="72">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="72">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="72">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="72">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="72">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="72" t="s">
         <v>164</v>
       </c>
-      <c r="Y22" s="72">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="72">
-        <v>1</v>
-      </c>
-      <c r="AA22" s="72">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="72">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="72">
-        <v>0</v>
-      </c>
-      <c r="AD22" s="72">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="72">
-        <v>0</v>
-      </c>
-      <c r="AF22" s="72">
-        <v>0</v>
-      </c>
-      <c r="AG22" s="72" t="s">
+      <c r="AH22" s="72">
+        <v>1</v>
+      </c>
+      <c r="AI22" s="72">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="72">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="72">
+        <v>0</v>
+      </c>
+      <c r="AL22" s="72">
+        <v>0</v>
+      </c>
+      <c r="AM22" s="72">
+        <v>0</v>
+      </c>
+      <c r="AN22" s="72">
+        <v>0</v>
+      </c>
+      <c r="AO22" s="72">
+        <v>0</v>
+      </c>
+      <c r="AP22" s="72">
+        <v>0</v>
+      </c>
+      <c r="AQ22" s="72" t="s">
         <v>165</v>
-      </c>
-      <c r="AH22" s="72">
-        <v>1</v>
-      </c>
-      <c r="AI22" s="72">
-        <v>0</v>
-      </c>
-      <c r="AJ22" s="72">
-        <v>0</v>
-      </c>
-      <c r="AK22" s="72">
-        <v>0</v>
-      </c>
-      <c r="AL22" s="72">
-        <v>0</v>
-      </c>
-      <c r="AM22" s="72">
-        <v>0</v>
-      </c>
-      <c r="AN22" s="72">
-        <v>0</v>
-      </c>
-      <c r="AO22" s="72">
-        <v>0</v>
-      </c>
-      <c r="AP22" s="72">
-        <v>0</v>
-      </c>
-      <c r="AQ22" s="72" t="s">
-        <v>166</v>
       </c>
       <c r="AR22" s="72" t="s">
         <v>105</v>
       </c>
       <c r="AS22" s="74" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AT22" s="72" t="s">
         <v>83</v>
@@ -8099,16 +8193,16 @@
         <v>513</v>
       </c>
       <c r="E23" s="72" t="s">
-        <v>159</v>
+        <v>482</v>
       </c>
       <c r="F23" s="72">
         <v>2023</v>
       </c>
       <c r="G23" s="72" t="s">
+        <v>159</v>
+      </c>
+      <c r="H23" s="72" t="s">
         <v>160</v>
-      </c>
-      <c r="H23" s="72" t="s">
-        <v>161</v>
       </c>
       <c r="I23" s="72">
         <v>2</v>
@@ -8117,13 +8211,13 @@
         <v>2018</v>
       </c>
       <c r="M23" s="72" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N23" s="72" t="s">
         <v>102</v>
       </c>
       <c r="O23" s="72" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P23" s="72" t="s">
         <v>87</v>
@@ -8150,70 +8244,70 @@
         <v>95</v>
       </c>
       <c r="X23" s="72" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y23" s="72">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="72">
+        <v>1</v>
+      </c>
+      <c r="AA23" s="72">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="72">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="72">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="72">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="72">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="72">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="72" t="s">
         <v>164</v>
       </c>
-      <c r="Y23" s="72">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="72">
-        <v>1</v>
-      </c>
-      <c r="AA23" s="72">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="72">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="72">
-        <v>0</v>
-      </c>
-      <c r="AD23" s="72">
-        <v>0</v>
-      </c>
-      <c r="AE23" s="72">
-        <v>0</v>
-      </c>
-      <c r="AF23" s="72">
-        <v>0</v>
-      </c>
-      <c r="AG23" s="72" t="s">
+      <c r="AH23" s="72">
+        <v>1</v>
+      </c>
+      <c r="AI23" s="72">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="72">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="72">
+        <v>0</v>
+      </c>
+      <c r="AL23" s="72">
+        <v>0</v>
+      </c>
+      <c r="AM23" s="72">
+        <v>0</v>
+      </c>
+      <c r="AN23" s="72">
+        <v>0</v>
+      </c>
+      <c r="AO23" s="72">
+        <v>0</v>
+      </c>
+      <c r="AP23" s="72">
+        <v>0</v>
+      </c>
+      <c r="AQ23" s="72" t="s">
         <v>165</v>
-      </c>
-      <c r="AH23" s="72">
-        <v>1</v>
-      </c>
-      <c r="AI23" s="72">
-        <v>0</v>
-      </c>
-      <c r="AJ23" s="72">
-        <v>0</v>
-      </c>
-      <c r="AK23" s="72">
-        <v>0</v>
-      </c>
-      <c r="AL23" s="72">
-        <v>0</v>
-      </c>
-      <c r="AM23" s="72">
-        <v>0</v>
-      </c>
-      <c r="AN23" s="72">
-        <v>0</v>
-      </c>
-      <c r="AO23" s="72">
-        <v>0</v>
-      </c>
-      <c r="AP23" s="72">
-        <v>0</v>
-      </c>
-      <c r="AQ23" s="72" t="s">
-        <v>166</v>
       </c>
       <c r="AR23" s="72" t="s">
         <v>105</v>
       </c>
       <c r="AS23" s="74" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AT23" s="72" t="s">
         <v>83</v>
@@ -8359,16 +8453,16 @@
         <v>513</v>
       </c>
       <c r="E24" s="72" t="s">
-        <v>159</v>
+        <v>482</v>
       </c>
       <c r="F24" s="72">
         <v>2023</v>
       </c>
       <c r="G24" s="72" t="s">
+        <v>159</v>
+      </c>
+      <c r="H24" s="72" t="s">
         <v>160</v>
-      </c>
-      <c r="H24" s="72" t="s">
-        <v>161</v>
       </c>
       <c r="I24" s="72">
         <v>2</v>
@@ -8377,13 +8471,13 @@
         <v>2018</v>
       </c>
       <c r="M24" s="72" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N24" s="72" t="s">
         <v>102</v>
       </c>
       <c r="O24" s="72" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P24" s="72" t="s">
         <v>87</v>
@@ -8410,7 +8504,7 @@
         <v>95</v>
       </c>
       <c r="X24" s="72" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Y24" s="72">
         <v>0</v>
@@ -8437,7 +8531,7 @@
         <v>0</v>
       </c>
       <c r="AG24" s="72" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AH24" s="72">
         <v>1</v>
@@ -8467,13 +8561,13 @@
         <v>0</v>
       </c>
       <c r="AQ24" s="72" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AR24" s="72" t="s">
         <v>105</v>
       </c>
       <c r="AS24" s="74" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AT24" s="72" t="s">
         <v>83</v>
@@ -8553,7 +8647,7 @@
         <v>83</v>
       </c>
       <c r="BS24" s="72" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="BT24" s="72">
         <v>0</v>
@@ -8619,16 +8713,16 @@
         <v>513</v>
       </c>
       <c r="E25" s="72" t="s">
-        <v>159</v>
+        <v>482</v>
       </c>
       <c r="F25" s="72">
         <v>2023</v>
       </c>
       <c r="G25" s="72" t="s">
+        <v>159</v>
+      </c>
+      <c r="H25" s="72" t="s">
         <v>160</v>
-      </c>
-      <c r="H25" s="72" t="s">
-        <v>161</v>
       </c>
       <c r="I25" s="72">
         <v>2</v>
@@ -8637,13 +8731,13 @@
         <v>2018</v>
       </c>
       <c r="M25" s="72" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N25" s="72" t="s">
         <v>102</v>
       </c>
       <c r="O25" s="72" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P25" s="72" t="s">
         <v>87</v>
@@ -8670,7 +8764,7 @@
         <v>95</v>
       </c>
       <c r="X25" s="72" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Y25" s="72">
         <v>0</v>
@@ -8697,7 +8791,7 @@
         <v>0</v>
       </c>
       <c r="AG25" s="72" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AH25" s="72">
         <v>1</v>
@@ -8727,13 +8821,13 @@
         <v>0</v>
       </c>
       <c r="AQ25" s="72" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AR25" s="72" t="s">
         <v>105</v>
       </c>
       <c r="AS25" s="74" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AT25" s="72" t="s">
         <v>83</v>
@@ -8813,7 +8907,7 @@
         <v>83</v>
       </c>
       <c r="BS25" s="72" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="BT25" s="72">
         <v>0</v>
@@ -8879,16 +8973,16 @@
         <v>513</v>
       </c>
       <c r="E26" s="72" t="s">
-        <v>159</v>
+        <v>482</v>
       </c>
       <c r="F26" s="72">
         <v>2023</v>
       </c>
       <c r="G26" s="72" t="s">
+        <v>159</v>
+      </c>
+      <c r="H26" s="72" t="s">
         <v>160</v>
-      </c>
-      <c r="H26" s="72" t="s">
-        <v>161</v>
       </c>
       <c r="I26" s="72">
         <v>2</v>
@@ -8897,13 +8991,13 @@
         <v>2018</v>
       </c>
       <c r="M26" s="72" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N26" s="72" t="s">
         <v>102</v>
       </c>
       <c r="O26" s="72" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P26" s="72" t="s">
         <v>87</v>
@@ -8930,70 +9024,70 @@
         <v>95</v>
       </c>
       <c r="X26" s="72" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y26" s="72">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="72">
+        <v>1</v>
+      </c>
+      <c r="AA26" s="72">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="72">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="72">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="72">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="72">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="72">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="72" t="s">
         <v>164</v>
       </c>
-      <c r="Y26" s="72">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="72">
-        <v>1</v>
-      </c>
-      <c r="AA26" s="72">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="72">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="72">
-        <v>0</v>
-      </c>
-      <c r="AD26" s="72">
-        <v>0</v>
-      </c>
-      <c r="AE26" s="72">
-        <v>0</v>
-      </c>
-      <c r="AF26" s="72">
-        <v>0</v>
-      </c>
-      <c r="AG26" s="72" t="s">
+      <c r="AH26" s="72">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="72">
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="72">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="72">
+        <v>1</v>
+      </c>
+      <c r="AL26" s="72">
+        <v>0</v>
+      </c>
+      <c r="AM26" s="72">
+        <v>0</v>
+      </c>
+      <c r="AN26" s="72">
+        <v>0</v>
+      </c>
+      <c r="AO26" s="72">
+        <v>0</v>
+      </c>
+      <c r="AP26" s="72">
+        <v>0</v>
+      </c>
+      <c r="AQ26" s="72" t="s">
         <v>165</v>
-      </c>
-      <c r="AH26" s="72">
-        <v>0</v>
-      </c>
-      <c r="AI26" s="72">
-        <v>0</v>
-      </c>
-      <c r="AJ26" s="72">
-        <v>0</v>
-      </c>
-      <c r="AK26" s="72">
-        <v>1</v>
-      </c>
-      <c r="AL26" s="72">
-        <v>0</v>
-      </c>
-      <c r="AM26" s="72">
-        <v>0</v>
-      </c>
-      <c r="AN26" s="72">
-        <v>0</v>
-      </c>
-      <c r="AO26" s="72">
-        <v>0</v>
-      </c>
-      <c r="AP26" s="72">
-        <v>0</v>
-      </c>
-      <c r="AQ26" s="72" t="s">
-        <v>166</v>
       </c>
       <c r="AR26" s="72" t="s">
         <v>105</v>
       </c>
       <c r="AS26" s="74" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AT26" s="72" t="s">
         <v>83</v>
@@ -9139,16 +9233,16 @@
         <v>513</v>
       </c>
       <c r="E27" s="72" t="s">
-        <v>159</v>
+        <v>482</v>
       </c>
       <c r="F27" s="72">
         <v>2023</v>
       </c>
       <c r="G27" s="72" t="s">
+        <v>159</v>
+      </c>
+      <c r="H27" s="72" t="s">
         <v>160</v>
-      </c>
-      <c r="H27" s="72" t="s">
-        <v>161</v>
       </c>
       <c r="I27" s="72">
         <v>2</v>
@@ -9157,13 +9251,13 @@
         <v>2018</v>
       </c>
       <c r="M27" s="72" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N27" s="72" t="s">
         <v>102</v>
       </c>
       <c r="O27" s="72" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P27" s="72" t="s">
         <v>87</v>
@@ -9190,70 +9284,70 @@
         <v>95</v>
       </c>
       <c r="X27" s="72" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y27" s="72">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="72">
+        <v>1</v>
+      </c>
+      <c r="AA27" s="72">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="72">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="72">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="72">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="72">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="72">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="72" t="s">
         <v>164</v>
       </c>
-      <c r="Y27" s="72">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="72">
-        <v>1</v>
-      </c>
-      <c r="AA27" s="72">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="72">
-        <v>0</v>
-      </c>
-      <c r="AC27" s="72">
-        <v>0</v>
-      </c>
-      <c r="AD27" s="72">
-        <v>0</v>
-      </c>
-      <c r="AE27" s="72">
-        <v>0</v>
-      </c>
-      <c r="AF27" s="72">
-        <v>0</v>
-      </c>
-      <c r="AG27" s="72" t="s">
+      <c r="AH27" s="72">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="72">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="72">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="72">
+        <v>1</v>
+      </c>
+      <c r="AL27" s="72">
+        <v>0</v>
+      </c>
+      <c r="AM27" s="72">
+        <v>0</v>
+      </c>
+      <c r="AN27" s="72">
+        <v>0</v>
+      </c>
+      <c r="AO27" s="72">
+        <v>0</v>
+      </c>
+      <c r="AP27" s="72">
+        <v>0</v>
+      </c>
+      <c r="AQ27" s="72" t="s">
         <v>165</v>
-      </c>
-      <c r="AH27" s="72">
-        <v>0</v>
-      </c>
-      <c r="AI27" s="72">
-        <v>0</v>
-      </c>
-      <c r="AJ27" s="72">
-        <v>0</v>
-      </c>
-      <c r="AK27" s="72">
-        <v>1</v>
-      </c>
-      <c r="AL27" s="72">
-        <v>0</v>
-      </c>
-      <c r="AM27" s="72">
-        <v>0</v>
-      </c>
-      <c r="AN27" s="72">
-        <v>0</v>
-      </c>
-      <c r="AO27" s="72">
-        <v>0</v>
-      </c>
-      <c r="AP27" s="72">
-        <v>0</v>
-      </c>
-      <c r="AQ27" s="72" t="s">
-        <v>166</v>
       </c>
       <c r="AR27" s="72" t="s">
         <v>105</v>
       </c>
       <c r="AS27" s="74" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AT27" s="72" t="s">
         <v>83</v>
@@ -9399,16 +9493,16 @@
         <v>513</v>
       </c>
       <c r="E28" s="72" t="s">
-        <v>159</v>
+        <v>482</v>
       </c>
       <c r="F28" s="72">
         <v>2023</v>
       </c>
       <c r="G28" s="72" t="s">
+        <v>159</v>
+      </c>
+      <c r="H28" s="72" t="s">
         <v>160</v>
-      </c>
-      <c r="H28" s="72" t="s">
-        <v>161</v>
       </c>
       <c r="I28" s="72">
         <v>2</v>
@@ -9417,13 +9511,13 @@
         <v>2018</v>
       </c>
       <c r="M28" s="72" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N28" s="72" t="s">
         <v>102</v>
       </c>
       <c r="O28" s="72" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P28" s="72" t="s">
         <v>87</v>
@@ -9450,7 +9544,7 @@
         <v>95</v>
       </c>
       <c r="X28" s="72" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Y28" s="72">
         <v>0</v>
@@ -9477,7 +9571,7 @@
         <v>0</v>
       </c>
       <c r="AG28" s="72" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AH28" s="72">
         <v>0</v>
@@ -9507,13 +9601,13 @@
         <v>0</v>
       </c>
       <c r="AQ28" s="72" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AR28" s="72" t="s">
         <v>105</v>
       </c>
       <c r="AS28" s="74" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AT28" s="72" t="s">
         <v>83</v>
@@ -9593,7 +9687,7 @@
         <v>83</v>
       </c>
       <c r="BS28" s="72" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="BT28" s="72">
         <v>0</v>
@@ -9659,16 +9753,16 @@
         <v>513</v>
       </c>
       <c r="E29" s="72" t="s">
-        <v>159</v>
+        <v>482</v>
       </c>
       <c r="F29" s="72">
         <v>2023</v>
       </c>
       <c r="G29" s="72" t="s">
+        <v>159</v>
+      </c>
+      <c r="H29" s="72" t="s">
         <v>160</v>
-      </c>
-      <c r="H29" s="72" t="s">
-        <v>161</v>
       </c>
       <c r="I29" s="72">
         <v>2</v>
@@ -9677,13 +9771,13 @@
         <v>2018</v>
       </c>
       <c r="M29" s="72" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N29" s="72" t="s">
         <v>102</v>
       </c>
       <c r="O29" s="72" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P29" s="72" t="s">
         <v>87</v>
@@ -9710,7 +9804,7 @@
         <v>95</v>
       </c>
       <c r="X29" s="72" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Y29" s="72">
         <v>0</v>
@@ -9737,7 +9831,7 @@
         <v>0</v>
       </c>
       <c r="AG29" s="72" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AH29" s="72">
         <v>0</v>
@@ -9767,13 +9861,13 @@
         <v>0</v>
       </c>
       <c r="AQ29" s="72" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AR29" s="72" t="s">
         <v>105</v>
       </c>
       <c r="AS29" s="74" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AT29" s="72" t="s">
         <v>83</v>
@@ -9853,7 +9947,7 @@
         <v>83</v>
       </c>
       <c r="BS29" s="72" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="BT29" s="72">
         <v>0</v>
@@ -9919,16 +10013,16 @@
         <v>513</v>
       </c>
       <c r="E30" s="72" t="s">
-        <v>159</v>
+        <v>482</v>
       </c>
       <c r="F30" s="72">
         <v>2023</v>
       </c>
       <c r="G30" s="72" t="s">
+        <v>159</v>
+      </c>
+      <c r="H30" s="72" t="s">
         <v>160</v>
-      </c>
-      <c r="H30" s="72" t="s">
-        <v>161</v>
       </c>
       <c r="I30" s="72">
         <v>2</v>
@@ -9937,13 +10031,13 @@
         <v>2018</v>
       </c>
       <c r="M30" s="72" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N30" s="72" t="s">
         <v>102</v>
       </c>
       <c r="O30" s="72" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P30" s="72" t="s">
         <v>87</v>
@@ -9970,70 +10064,70 @@
         <v>95</v>
       </c>
       <c r="X30" s="72" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y30" s="72">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="72">
+        <v>1</v>
+      </c>
+      <c r="AA30" s="72">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="72">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="72">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="72">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="72">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="72">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="72" t="s">
         <v>164</v>
       </c>
-      <c r="Y30" s="72">
-        <v>0</v>
-      </c>
-      <c r="Z30" s="72">
-        <v>1</v>
-      </c>
-      <c r="AA30" s="72">
-        <v>0</v>
-      </c>
-      <c r="AB30" s="72">
-        <v>0</v>
-      </c>
-      <c r="AC30" s="72">
-        <v>0</v>
-      </c>
-      <c r="AD30" s="72">
-        <v>0</v>
-      </c>
-      <c r="AE30" s="72">
-        <v>0</v>
-      </c>
-      <c r="AF30" s="72">
-        <v>0</v>
-      </c>
-      <c r="AG30" s="72" t="s">
+      <c r="AH30" s="72">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="72">
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="72">
+        <v>1</v>
+      </c>
+      <c r="AK30" s="72">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="72">
+        <v>0</v>
+      </c>
+      <c r="AM30" s="72">
+        <v>0</v>
+      </c>
+      <c r="AN30" s="72">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="72">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="72">
+        <v>0</v>
+      </c>
+      <c r="AQ30" s="72" t="s">
         <v>165</v>
-      </c>
-      <c r="AH30" s="72">
-        <v>0</v>
-      </c>
-      <c r="AI30" s="72">
-        <v>0</v>
-      </c>
-      <c r="AJ30" s="72">
-        <v>1</v>
-      </c>
-      <c r="AK30" s="72">
-        <v>0</v>
-      </c>
-      <c r="AL30" s="72">
-        <v>0</v>
-      </c>
-      <c r="AM30" s="72">
-        <v>0</v>
-      </c>
-      <c r="AN30" s="72">
-        <v>0</v>
-      </c>
-      <c r="AO30" s="72">
-        <v>0</v>
-      </c>
-      <c r="AP30" s="72">
-        <v>0</v>
-      </c>
-      <c r="AQ30" s="72" t="s">
-        <v>166</v>
       </c>
       <c r="AR30" s="72" t="s">
         <v>105</v>
       </c>
       <c r="AS30" s="74" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AT30" s="72" t="s">
         <v>83</v>
@@ -10179,16 +10273,16 @@
         <v>513</v>
       </c>
       <c r="E31" s="72" t="s">
-        <v>159</v>
+        <v>482</v>
       </c>
       <c r="F31" s="72">
         <v>2023</v>
       </c>
       <c r="G31" s="72" t="s">
+        <v>159</v>
+      </c>
+      <c r="H31" s="72" t="s">
         <v>160</v>
-      </c>
-      <c r="H31" s="72" t="s">
-        <v>161</v>
       </c>
       <c r="I31" s="72">
         <v>2</v>
@@ -10197,13 +10291,13 @@
         <v>2018</v>
       </c>
       <c r="M31" s="72" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N31" s="72" t="s">
         <v>102</v>
       </c>
       <c r="O31" s="72" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P31" s="72" t="s">
         <v>87</v>
@@ -10230,70 +10324,70 @@
         <v>95</v>
       </c>
       <c r="X31" s="72" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y31" s="72">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="72">
+        <v>1</v>
+      </c>
+      <c r="AA31" s="72">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="72">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="72">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="72">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="72">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="72">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="72" t="s">
         <v>164</v>
       </c>
-      <c r="Y31" s="72">
-        <v>0</v>
-      </c>
-      <c r="Z31" s="72">
-        <v>1</v>
-      </c>
-      <c r="AA31" s="72">
-        <v>0</v>
-      </c>
-      <c r="AB31" s="72">
-        <v>0</v>
-      </c>
-      <c r="AC31" s="72">
-        <v>0</v>
-      </c>
-      <c r="AD31" s="72">
-        <v>0</v>
-      </c>
-      <c r="AE31" s="72">
-        <v>0</v>
-      </c>
-      <c r="AF31" s="72">
-        <v>0</v>
-      </c>
-      <c r="AG31" s="72" t="s">
+      <c r="AH31" s="72">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="72">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="72">
+        <v>1</v>
+      </c>
+      <c r="AK31" s="72">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="72">
+        <v>0</v>
+      </c>
+      <c r="AM31" s="72">
+        <v>0</v>
+      </c>
+      <c r="AN31" s="72">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="72">
+        <v>0</v>
+      </c>
+      <c r="AP31" s="72">
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="72" t="s">
         <v>165</v>
-      </c>
-      <c r="AH31" s="72">
-        <v>0</v>
-      </c>
-      <c r="AI31" s="72">
-        <v>0</v>
-      </c>
-      <c r="AJ31" s="72">
-        <v>1</v>
-      </c>
-      <c r="AK31" s="72">
-        <v>0</v>
-      </c>
-      <c r="AL31" s="72">
-        <v>0</v>
-      </c>
-      <c r="AM31" s="72">
-        <v>0</v>
-      </c>
-      <c r="AN31" s="72">
-        <v>0</v>
-      </c>
-      <c r="AO31" s="72">
-        <v>0</v>
-      </c>
-      <c r="AP31" s="72">
-        <v>0</v>
-      </c>
-      <c r="AQ31" s="72" t="s">
-        <v>166</v>
       </c>
       <c r="AR31" s="72" t="s">
         <v>105</v>
       </c>
       <c r="AS31" s="74" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AT31" s="72" t="s">
         <v>83</v>
@@ -10439,16 +10533,16 @@
         <v>513</v>
       </c>
       <c r="E32" s="72" t="s">
-        <v>159</v>
+        <v>482</v>
       </c>
       <c r="F32" s="72">
         <v>2023</v>
       </c>
       <c r="G32" s="72" t="s">
+        <v>159</v>
+      </c>
+      <c r="H32" s="72" t="s">
         <v>160</v>
-      </c>
-      <c r="H32" s="72" t="s">
-        <v>161</v>
       </c>
       <c r="I32" s="72">
         <v>2</v>
@@ -10457,13 +10551,13 @@
         <v>2018</v>
       </c>
       <c r="M32" s="72" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N32" s="72" t="s">
         <v>102</v>
       </c>
       <c r="O32" s="72" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P32" s="72" t="s">
         <v>87</v>
@@ -10490,7 +10584,7 @@
         <v>95</v>
       </c>
       <c r="X32" s="72" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Y32" s="72">
         <v>0</v>
@@ -10517,7 +10611,7 @@
         <v>0</v>
       </c>
       <c r="AG32" s="72" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AH32" s="72">
         <v>0</v>
@@ -10547,13 +10641,13 @@
         <v>0</v>
       </c>
       <c r="AQ32" s="72" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AR32" s="72" t="s">
         <v>105</v>
       </c>
       <c r="AS32" s="74" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AT32" s="72" t="s">
         <v>83</v>
@@ -10633,7 +10727,7 @@
         <v>83</v>
       </c>
       <c r="BS32" s="91" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="BT32" s="91">
         <v>0</v>
@@ -10699,16 +10793,16 @@
         <v>513</v>
       </c>
       <c r="E33" s="72" t="s">
-        <v>159</v>
+        <v>482</v>
       </c>
       <c r="F33" s="72">
         <v>2023</v>
       </c>
       <c r="G33" s="72" t="s">
+        <v>159</v>
+      </c>
+      <c r="H33" s="72" t="s">
         <v>160</v>
-      </c>
-      <c r="H33" s="72" t="s">
-        <v>161</v>
       </c>
       <c r="I33" s="72">
         <v>2</v>
@@ -10717,13 +10811,13 @@
         <v>2018</v>
       </c>
       <c r="M33" s="72" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N33" s="72" t="s">
         <v>102</v>
       </c>
       <c r="O33" s="72" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P33" s="72" t="s">
         <v>87</v>
@@ -10750,7 +10844,7 @@
         <v>95</v>
       </c>
       <c r="X33" s="72" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Y33" s="72">
         <v>0</v>
@@ -10777,7 +10871,7 @@
         <v>0</v>
       </c>
       <c r="AG33" s="72" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AH33" s="72">
         <v>0</v>
@@ -10807,13 +10901,13 @@
         <v>0</v>
       </c>
       <c r="AQ33" s="72" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AR33" s="72" t="s">
         <v>105</v>
       </c>
       <c r="AS33" s="74" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AT33" s="72" t="s">
         <v>83</v>
@@ -10893,7 +10987,7 @@
         <v>83</v>
       </c>
       <c r="BS33" s="91" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="BT33" s="91">
         <v>0</v>
@@ -10959,16 +11053,16 @@
         <v>513</v>
       </c>
       <c r="E34" s="72" t="s">
-        <v>159</v>
+        <v>482</v>
       </c>
       <c r="F34" s="72">
         <v>2023</v>
       </c>
       <c r="G34" s="72" t="s">
+        <v>159</v>
+      </c>
+      <c r="H34" s="72" t="s">
         <v>160</v>
-      </c>
-      <c r="H34" s="72" t="s">
-        <v>161</v>
       </c>
       <c r="I34" s="72">
         <v>2</v>
@@ -10977,13 +11071,13 @@
         <v>2018</v>
       </c>
       <c r="M34" s="72" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N34" s="72" t="s">
         <v>102</v>
       </c>
       <c r="O34" s="72" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P34" s="72" t="s">
         <v>87</v>
@@ -11010,70 +11104,70 @@
         <v>95</v>
       </c>
       <c r="X34" s="72" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y34" s="72">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="72">
+        <v>1</v>
+      </c>
+      <c r="AA34" s="72">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="72">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="72">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="72">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="72">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="72">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="72" t="s">
         <v>164</v>
       </c>
-      <c r="Y34" s="72">
-        <v>0</v>
-      </c>
-      <c r="Z34" s="72">
-        <v>1</v>
-      </c>
-      <c r="AA34" s="72">
-        <v>0</v>
-      </c>
-      <c r="AB34" s="72">
-        <v>0</v>
-      </c>
-      <c r="AC34" s="72">
-        <v>0</v>
-      </c>
-      <c r="AD34" s="72">
-        <v>0</v>
-      </c>
-      <c r="AE34" s="72">
-        <v>0</v>
-      </c>
-      <c r="AF34" s="72">
-        <v>0</v>
-      </c>
-      <c r="AG34" s="72" t="s">
+      <c r="AH34" s="72">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="72">
+        <v>1</v>
+      </c>
+      <c r="AJ34" s="72">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="72">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="72">
+        <v>0</v>
+      </c>
+      <c r="AM34" s="72">
+        <v>0</v>
+      </c>
+      <c r="AN34" s="72">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="72">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="72">
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="72" t="s">
         <v>165</v>
-      </c>
-      <c r="AH34" s="72">
-        <v>0</v>
-      </c>
-      <c r="AI34" s="72">
-        <v>1</v>
-      </c>
-      <c r="AJ34" s="72">
-        <v>0</v>
-      </c>
-      <c r="AK34" s="72">
-        <v>0</v>
-      </c>
-      <c r="AL34" s="72">
-        <v>0</v>
-      </c>
-      <c r="AM34" s="72">
-        <v>0</v>
-      </c>
-      <c r="AN34" s="72">
-        <v>0</v>
-      </c>
-      <c r="AO34" s="72">
-        <v>0</v>
-      </c>
-      <c r="AP34" s="72">
-        <v>0</v>
-      </c>
-      <c r="AQ34" s="72" t="s">
-        <v>166</v>
       </c>
       <c r="AR34" s="72" t="s">
         <v>105</v>
       </c>
       <c r="AS34" s="74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AT34" s="72" t="s">
         <v>83</v>
@@ -11219,16 +11313,16 @@
         <v>513</v>
       </c>
       <c r="E35" s="72" t="s">
-        <v>159</v>
+        <v>482</v>
       </c>
       <c r="F35" s="72">
         <v>2023</v>
       </c>
       <c r="G35" s="72" t="s">
+        <v>159</v>
+      </c>
+      <c r="H35" s="72" t="s">
         <v>160</v>
-      </c>
-      <c r="H35" s="72" t="s">
-        <v>161</v>
       </c>
       <c r="I35" s="72">
         <v>2</v>
@@ -11237,13 +11331,13 @@
         <v>2018</v>
       </c>
       <c r="M35" s="72" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N35" s="72" t="s">
         <v>102</v>
       </c>
       <c r="O35" s="72" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P35" s="72" t="s">
         <v>87</v>
@@ -11270,70 +11364,70 @@
         <v>95</v>
       </c>
       <c r="X35" s="72" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y35" s="72">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="72">
+        <v>1</v>
+      </c>
+      <c r="AA35" s="72">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="72">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="72">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="72">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="72">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="72">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="72" t="s">
         <v>164</v>
       </c>
-      <c r="Y35" s="72">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="72">
-        <v>1</v>
-      </c>
-      <c r="AA35" s="72">
-        <v>0</v>
-      </c>
-      <c r="AB35" s="72">
-        <v>0</v>
-      </c>
-      <c r="AC35" s="72">
-        <v>0</v>
-      </c>
-      <c r="AD35" s="72">
-        <v>0</v>
-      </c>
-      <c r="AE35" s="72">
-        <v>0</v>
-      </c>
-      <c r="AF35" s="72">
-        <v>0</v>
-      </c>
-      <c r="AG35" s="72" t="s">
+      <c r="AH35" s="72">
+        <v>0</v>
+      </c>
+      <c r="AI35" s="72">
+        <v>1</v>
+      </c>
+      <c r="AJ35" s="72">
+        <v>0</v>
+      </c>
+      <c r="AK35" s="72">
+        <v>0</v>
+      </c>
+      <c r="AL35" s="72">
+        <v>0</v>
+      </c>
+      <c r="AM35" s="72">
+        <v>0</v>
+      </c>
+      <c r="AN35" s="72">
+        <v>0</v>
+      </c>
+      <c r="AO35" s="72">
+        <v>0</v>
+      </c>
+      <c r="AP35" s="72">
+        <v>0</v>
+      </c>
+      <c r="AQ35" s="72" t="s">
         <v>165</v>
-      </c>
-      <c r="AH35" s="72">
-        <v>0</v>
-      </c>
-      <c r="AI35" s="72">
-        <v>1</v>
-      </c>
-      <c r="AJ35" s="72">
-        <v>0</v>
-      </c>
-      <c r="AK35" s="72">
-        <v>0</v>
-      </c>
-      <c r="AL35" s="72">
-        <v>0</v>
-      </c>
-      <c r="AM35" s="72">
-        <v>0</v>
-      </c>
-      <c r="AN35" s="72">
-        <v>0</v>
-      </c>
-      <c r="AO35" s="72">
-        <v>0</v>
-      </c>
-      <c r="AP35" s="72">
-        <v>0</v>
-      </c>
-      <c r="AQ35" s="72" t="s">
-        <v>166</v>
       </c>
       <c r="AR35" s="72" t="s">
         <v>105</v>
       </c>
       <c r="AS35" s="74" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AT35" s="72" t="s">
         <v>83</v>
@@ -11479,16 +11573,16 @@
         <v>513</v>
       </c>
       <c r="E36" s="72" t="s">
-        <v>159</v>
+        <v>482</v>
       </c>
       <c r="F36" s="72">
         <v>2023</v>
       </c>
       <c r="G36" s="72" t="s">
+        <v>159</v>
+      </c>
+      <c r="H36" s="72" t="s">
         <v>160</v>
-      </c>
-      <c r="H36" s="72" t="s">
-        <v>161</v>
       </c>
       <c r="I36" s="72">
         <v>2</v>
@@ -11497,13 +11591,13 @@
         <v>2018</v>
       </c>
       <c r="M36" s="72" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N36" s="72" t="s">
         <v>102</v>
       </c>
       <c r="O36" s="72" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P36" s="72" t="s">
         <v>87</v>
@@ -11530,7 +11624,7 @@
         <v>95</v>
       </c>
       <c r="X36" s="72" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Y36" s="72">
         <v>0</v>
@@ -11557,7 +11651,7 @@
         <v>0</v>
       </c>
       <c r="AG36" s="72" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AH36" s="72">
         <v>0</v>
@@ -11587,13 +11681,13 @@
         <v>0</v>
       </c>
       <c r="AQ36" s="72" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AR36" s="72" t="s">
         <v>105</v>
       </c>
       <c r="AS36" s="74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AT36" s="72" t="s">
         <v>83</v>
@@ -11673,7 +11767,7 @@
         <v>83</v>
       </c>
       <c r="BS36" s="72" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="BT36" s="72">
         <v>0</v>
@@ -11739,16 +11833,16 @@
         <v>513</v>
       </c>
       <c r="E37" s="72" t="s">
-        <v>159</v>
+        <v>482</v>
       </c>
       <c r="F37" s="72">
         <v>2023</v>
       </c>
       <c r="G37" s="72" t="s">
+        <v>159</v>
+      </c>
+      <c r="H37" s="72" t="s">
         <v>160</v>
-      </c>
-      <c r="H37" s="72" t="s">
-        <v>161</v>
       </c>
       <c r="I37" s="72">
         <v>2</v>
@@ -11757,13 +11851,13 @@
         <v>2018</v>
       </c>
       <c r="M37" s="72" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N37" s="72" t="s">
         <v>102</v>
       </c>
       <c r="O37" s="72" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P37" s="72" t="s">
         <v>87</v>
@@ -11790,7 +11884,7 @@
         <v>95</v>
       </c>
       <c r="X37" s="72" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Y37" s="72">
         <v>0</v>
@@ -11817,7 +11911,7 @@
         <v>0</v>
       </c>
       <c r="AG37" s="72" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AH37" s="72">
         <v>0</v>
@@ -11847,13 +11941,13 @@
         <v>0</v>
       </c>
       <c r="AQ37" s="72" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AR37" s="72" t="s">
         <v>105</v>
       </c>
       <c r="AS37" s="74" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AT37" s="72" t="s">
         <v>83</v>
@@ -11933,7 +12027,7 @@
         <v>83</v>
       </c>
       <c r="BS37" s="72" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="BT37" s="72">
         <v>0</v>
@@ -11998,22 +12092,22 @@
         <v>514</v>
       </c>
       <c r="E38" s="110" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F38" s="110">
         <v>2025</v>
       </c>
       <c r="G38" s="110" t="s">
+        <v>177</v>
+      </c>
+      <c r="H38" s="110" t="s">
         <v>178</v>
-      </c>
-      <c r="H38" s="110" t="s">
-        <v>179</v>
       </c>
       <c r="I38" s="110">
         <v>2</v>
       </c>
       <c r="J38" s="110" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K38" s="110" t="s">
         <v>158</v>
@@ -12037,16 +12131,16 @@
         <v>515</v>
       </c>
       <c r="E39" s="72" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F39" s="72">
         <v>2023</v>
       </c>
       <c r="G39" s="72" t="s">
+        <v>181</v>
+      </c>
+      <c r="H39" s="72" t="s">
         <v>182</v>
-      </c>
-      <c r="H39" s="72" t="s">
-        <v>183</v>
       </c>
       <c r="I39" s="72">
         <v>2</v>
@@ -12064,13 +12158,13 @@
         <v>102</v>
       </c>
       <c r="O39" s="72" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P39" s="72" t="s">
         <v>87</v>
       </c>
       <c r="Q39" s="72" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="R39" s="72" t="s">
         <v>109</v>
@@ -12154,10 +12248,10 @@
         <v>105</v>
       </c>
       <c r="AS39" s="72" t="s">
+        <v>185</v>
+      </c>
+      <c r="AT39" s="72" t="s">
         <v>186</v>
-      </c>
-      <c r="AT39" s="72" t="s">
-        <v>187</v>
       </c>
       <c r="AU39" s="78">
         <v>2.1000000000000001E-2</v>
@@ -12297,16 +12391,16 @@
         <v>515</v>
       </c>
       <c r="E40" s="72" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F40" s="72">
         <v>2023</v>
       </c>
       <c r="G40" s="72" t="s">
+        <v>181</v>
+      </c>
+      <c r="H40" s="72" t="s">
         <v>182</v>
-      </c>
-      <c r="H40" s="72" t="s">
-        <v>183</v>
       </c>
       <c r="I40" s="72">
         <v>2</v>
@@ -12324,13 +12418,13 @@
         <v>102</v>
       </c>
       <c r="O40" s="72" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P40" s="72" t="s">
         <v>87</v>
       </c>
       <c r="Q40" s="72" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="R40" s="72" t="s">
         <v>109</v>
@@ -12414,10 +12508,10 @@
         <v>105</v>
       </c>
       <c r="AS40" s="72" t="s">
+        <v>185</v>
+      </c>
+      <c r="AT40" s="72" t="s">
         <v>186</v>
-      </c>
-      <c r="AT40" s="72" t="s">
-        <v>187</v>
       </c>
       <c r="AU40" s="78">
         <v>2.3E-2</v>
@@ -12557,16 +12651,16 @@
         <v>515</v>
       </c>
       <c r="E41" s="72" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F41" s="72">
         <v>2023</v>
       </c>
       <c r="G41" s="72" t="s">
+        <v>181</v>
+      </c>
+      <c r="H41" s="72" t="s">
         <v>182</v>
-      </c>
-      <c r="H41" s="72" t="s">
-        <v>183</v>
       </c>
       <c r="I41" s="72">
         <v>2</v>
@@ -12584,13 +12678,13 @@
         <v>102</v>
       </c>
       <c r="O41" s="72" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P41" s="72" t="s">
         <v>87</v>
       </c>
       <c r="Q41" s="72" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="R41" s="72" t="s">
         <v>109</v>
@@ -12674,10 +12768,10 @@
         <v>105</v>
       </c>
       <c r="AS41" s="72" t="s">
+        <v>185</v>
+      </c>
+      <c r="AT41" s="72" t="s">
         <v>186</v>
-      </c>
-      <c r="AT41" s="72" t="s">
-        <v>187</v>
       </c>
       <c r="AU41" s="78">
         <v>2.5999999999999999E-2</v>
@@ -12817,16 +12911,16 @@
         <v>515</v>
       </c>
       <c r="E42" s="72" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F42" s="72">
         <v>2023</v>
       </c>
       <c r="G42" s="72" t="s">
+        <v>181</v>
+      </c>
+      <c r="H42" s="72" t="s">
         <v>182</v>
-      </c>
-      <c r="H42" s="72" t="s">
-        <v>183</v>
       </c>
       <c r="I42" s="72">
         <v>2</v>
@@ -12844,13 +12938,13 @@
         <v>102</v>
       </c>
       <c r="O42" s="72" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P42" s="72" t="s">
         <v>87</v>
       </c>
       <c r="Q42" s="72" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="R42" s="72" t="s">
         <v>109</v>
@@ -12934,10 +13028,10 @@
         <v>152</v>
       </c>
       <c r="AS42" s="72" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AT42" s="72" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AU42" s="78">
         <v>15.845000000000001</v>
@@ -13077,16 +13171,16 @@
         <v>515</v>
       </c>
       <c r="E43" s="72" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F43" s="72">
         <v>2023</v>
       </c>
       <c r="G43" s="72" t="s">
+        <v>181</v>
+      </c>
+      <c r="H43" s="72" t="s">
         <v>182</v>
-      </c>
-      <c r="H43" s="72" t="s">
-        <v>183</v>
       </c>
       <c r="I43" s="72">
         <v>2</v>
@@ -13104,13 +13198,13 @@
         <v>102</v>
       </c>
       <c r="O43" s="72" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P43" s="72" t="s">
         <v>87</v>
       </c>
       <c r="Q43" s="72" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="R43" s="72" t="s">
         <v>109</v>
@@ -13194,10 +13288,10 @@
         <v>152</v>
       </c>
       <c r="AS43" s="72" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AT43" s="72" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AU43" s="78">
         <v>16.456</v>
@@ -13336,16 +13430,16 @@
         <v>516</v>
       </c>
       <c r="E44" s="110" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F44" s="110">
         <v>2025</v>
       </c>
       <c r="G44" s="110" t="s">
+        <v>189</v>
+      </c>
+      <c r="H44" s="110" t="s">
         <v>190</v>
-      </c>
-      <c r="H44" s="110" t="s">
-        <v>191</v>
       </c>
       <c r="I44" s="110">
         <v>2</v>
@@ -13374,16 +13468,16 @@
         <v>517</v>
       </c>
       <c r="E45" s="110" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F45" s="110">
         <v>2022</v>
       </c>
       <c r="G45" s="110" t="s">
+        <v>192</v>
+      </c>
+      <c r="H45" s="110" t="s">
         <v>193</v>
-      </c>
-      <c r="H45" s="110" t="s">
-        <v>194</v>
       </c>
       <c r="I45" s="110">
         <v>2</v>
@@ -13413,16 +13507,16 @@
         <v>520</v>
       </c>
       <c r="E46" s="72" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F46" s="72">
         <v>2024</v>
       </c>
       <c r="G46" s="72" t="s">
+        <v>195</v>
+      </c>
+      <c r="H46" s="72" t="s">
         <v>196</v>
-      </c>
-      <c r="H46" s="72" t="s">
-        <v>197</v>
       </c>
       <c r="I46" s="72">
         <v>2</v>
@@ -13440,7 +13534,7 @@
         <v>85</v>
       </c>
       <c r="O46" s="72" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P46" s="72" t="s">
         <v>87</v>
@@ -13524,13 +13618,13 @@
         <v>0</v>
       </c>
       <c r="AQ46" s="72" t="s">
+        <v>198</v>
+      </c>
+      <c r="AR46" s="72" t="s">
         <v>199</v>
       </c>
-      <c r="AR46" s="72" t="s">
+      <c r="AS46" s="72" t="s">
         <v>200</v>
-      </c>
-      <c r="AS46" s="72" t="s">
-        <v>201</v>
       </c>
       <c r="AT46" s="72" t="s">
         <v>96</v>
@@ -13589,7 +13683,7 @@
         <v>83</v>
       </c>
       <c r="BL46" s="72" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="BN46" s="72" t="s">
         <v>119</v>
@@ -13673,16 +13767,16 @@
         <v>520</v>
       </c>
       <c r="E47" s="72" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F47" s="72">
         <v>2024</v>
       </c>
       <c r="G47" s="72" t="s">
+        <v>195</v>
+      </c>
+      <c r="H47" s="72" t="s">
         <v>196</v>
-      </c>
-      <c r="H47" s="72" t="s">
-        <v>197</v>
       </c>
       <c r="I47" s="72">
         <v>2</v>
@@ -13700,7 +13794,7 @@
         <v>85</v>
       </c>
       <c r="O47" s="72" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P47" s="72" t="s">
         <v>87</v>
@@ -13784,13 +13878,13 @@
         <v>0</v>
       </c>
       <c r="AQ47" s="72" t="s">
+        <v>198</v>
+      </c>
+      <c r="AR47" s="72" t="s">
         <v>199</v>
       </c>
-      <c r="AR47" s="72" t="s">
+      <c r="AS47" s="72" t="s">
         <v>200</v>
-      </c>
-      <c r="AS47" s="72" t="s">
-        <v>201</v>
       </c>
       <c r="AT47" s="72" t="s">
         <v>96</v>
@@ -13849,7 +13943,7 @@
         <v>83</v>
       </c>
       <c r="BL47" s="72" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="BN47" s="72" t="s">
         <v>119</v>
@@ -13933,16 +14027,16 @@
         <v>520</v>
       </c>
       <c r="E48" s="72" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F48" s="72">
         <v>2024</v>
       </c>
       <c r="G48" s="72" t="s">
+        <v>195</v>
+      </c>
+      <c r="H48" s="72" t="s">
         <v>196</v>
-      </c>
-      <c r="H48" s="72" t="s">
-        <v>197</v>
       </c>
       <c r="I48" s="72">
         <v>2</v>
@@ -13960,7 +14054,7 @@
         <v>85</v>
       </c>
       <c r="O48" s="72" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P48" s="72" t="s">
         <v>87</v>
@@ -14044,13 +14138,13 @@
         <v>0</v>
       </c>
       <c r="AQ48" s="72" t="s">
+        <v>198</v>
+      </c>
+      <c r="AR48" s="72" t="s">
         <v>199</v>
       </c>
-      <c r="AR48" s="72" t="s">
+      <c r="AS48" s="72" t="s">
         <v>200</v>
-      </c>
-      <c r="AS48" s="72" t="s">
-        <v>201</v>
       </c>
       <c r="AT48" s="72" t="s">
         <v>96</v>
@@ -14109,10 +14203,10 @@
         <v>83</v>
       </c>
       <c r="BL48" s="72" t="s">
+        <v>203</v>
+      </c>
+      <c r="BM48" s="72" t="s">
         <v>204</v>
-      </c>
-      <c r="BM48" s="72" t="s">
-        <v>205</v>
       </c>
       <c r="BN48" s="72" t="s">
         <v>119</v>
@@ -14184,7 +14278,7 @@
         <v>5.2722872763891163E-6</v>
       </c>
     </row>
-    <row r="49" spans="1:87" s="72" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:90" s="72" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="72" t="s">
         <v>115</v>
       </c>
@@ -14196,16 +14290,16 @@
         <v>520</v>
       </c>
       <c r="E49" s="72" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F49" s="72">
         <v>2024</v>
       </c>
       <c r="G49" s="72" t="s">
+        <v>195</v>
+      </c>
+      <c r="H49" s="72" t="s">
         <v>196</v>
-      </c>
-      <c r="H49" s="72" t="s">
-        <v>197</v>
       </c>
       <c r="I49" s="72">
         <v>2</v>
@@ -14223,7 +14317,7 @@
         <v>85</v>
       </c>
       <c r="O49" s="72" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P49" s="72" t="s">
         <v>87</v>
@@ -14307,13 +14401,13 @@
         <v>0</v>
       </c>
       <c r="AQ49" s="72" t="s">
+        <v>198</v>
+      </c>
+      <c r="AR49" s="72" t="s">
         <v>199</v>
       </c>
-      <c r="AR49" s="72" t="s">
+      <c r="AS49" s="72" t="s">
         <v>200</v>
-      </c>
-      <c r="AS49" s="72" t="s">
-        <v>201</v>
       </c>
       <c r="AT49" s="72" t="s">
         <v>96</v>
@@ -14372,7 +14466,7 @@
         <v>83</v>
       </c>
       <c r="BL49" s="72" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="BN49" s="72" t="s">
         <v>119</v>
@@ -14444,7 +14538,7 @@
         <v>5.2722872763891163E-6</v>
       </c>
     </row>
-    <row r="50" spans="1:87" s="72" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:90" s="72" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="72" t="s">
         <v>115</v>
       </c>
@@ -14456,16 +14550,16 @@
         <v>520</v>
       </c>
       <c r="E50" s="72" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F50" s="72">
         <v>2024</v>
       </c>
       <c r="G50" s="72" t="s">
+        <v>195</v>
+      </c>
+      <c r="H50" s="72" t="s">
         <v>196</v>
-      </c>
-      <c r="H50" s="72" t="s">
-        <v>197</v>
       </c>
       <c r="I50" s="72">
         <v>2</v>
@@ -14483,7 +14577,7 @@
         <v>85</v>
       </c>
       <c r="O50" s="72" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P50" s="72" t="s">
         <v>87</v>
@@ -14567,13 +14661,13 @@
         <v>0</v>
       </c>
       <c r="AQ50" s="72" t="s">
+        <v>198</v>
+      </c>
+      <c r="AR50" s="72" t="s">
         <v>199</v>
       </c>
-      <c r="AR50" s="72" t="s">
+      <c r="AS50" s="72" t="s">
         <v>200</v>
-      </c>
-      <c r="AS50" s="72" t="s">
-        <v>201</v>
       </c>
       <c r="AT50" s="72" t="s">
         <v>96</v>
@@ -14632,10 +14726,10 @@
         <v>83</v>
       </c>
       <c r="BL50" s="72" t="s">
+        <v>207</v>
+      </c>
+      <c r="BM50" s="72" t="s">
         <v>208</v>
-      </c>
-      <c r="BM50" s="72" t="s">
-        <v>209</v>
       </c>
       <c r="BN50" s="72" t="s">
         <v>119</v>
@@ -14707,7 +14801,7 @@
         <v>5.2722872763891163E-6</v>
       </c>
     </row>
-    <row r="51" spans="1:87" s="72" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:90" s="72" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="72" t="s">
         <v>115</v>
       </c>
@@ -14719,16 +14813,16 @@
         <v>520</v>
       </c>
       <c r="E51" s="72" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F51" s="72">
         <v>2024</v>
       </c>
       <c r="G51" s="72" t="s">
+        <v>195</v>
+      </c>
+      <c r="H51" s="72" t="s">
         <v>196</v>
-      </c>
-      <c r="H51" s="72" t="s">
-        <v>197</v>
       </c>
       <c r="I51" s="72">
         <v>2</v>
@@ -14746,7 +14840,7 @@
         <v>85</v>
       </c>
       <c r="O51" s="72" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P51" s="72" t="s">
         <v>87</v>
@@ -14830,13 +14924,13 @@
         <v>0</v>
       </c>
       <c r="AQ51" s="72" t="s">
+        <v>198</v>
+      </c>
+      <c r="AR51" s="72" t="s">
         <v>199</v>
       </c>
-      <c r="AR51" s="72" t="s">
+      <c r="AS51" s="72" t="s">
         <v>200</v>
-      </c>
-      <c r="AS51" s="72" t="s">
-        <v>201</v>
       </c>
       <c r="AT51" s="72" t="s">
         <v>96</v>
@@ -14895,10 +14989,10 @@
         <v>83</v>
       </c>
       <c r="BL51" s="72" t="s">
+        <v>207</v>
+      </c>
+      <c r="BM51" s="72" t="s">
         <v>208</v>
-      </c>
-      <c r="BM51" s="72" t="s">
-        <v>209</v>
       </c>
       <c r="BN51" s="72" t="s">
         <v>119</v>
@@ -14970,7 +15064,7 @@
         <v>5.2722872763891163E-6</v>
       </c>
     </row>
-    <row r="52" spans="1:87" s="72" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:90" s="72" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="72" t="s">
         <v>115</v>
       </c>
@@ -14982,16 +15076,16 @@
         <v>520</v>
       </c>
       <c r="E52" s="72" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F52" s="72">
         <v>2024</v>
       </c>
       <c r="G52" s="72" t="s">
+        <v>195</v>
+      </c>
+      <c r="H52" s="72" t="s">
         <v>196</v>
-      </c>
-      <c r="H52" s="72" t="s">
-        <v>197</v>
       </c>
       <c r="I52" s="72">
         <v>2</v>
@@ -15009,7 +15103,7 @@
         <v>85</v>
       </c>
       <c r="O52" s="72" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P52" s="72" t="s">
         <v>87</v>
@@ -15093,13 +15187,13 @@
         <v>0</v>
       </c>
       <c r="AQ52" s="72" t="s">
+        <v>198</v>
+      </c>
+      <c r="AR52" s="72" t="s">
         <v>199</v>
       </c>
-      <c r="AR52" s="72" t="s">
+      <c r="AS52" s="72" t="s">
         <v>200</v>
-      </c>
-      <c r="AS52" s="72" t="s">
-        <v>201</v>
       </c>
       <c r="AT52" s="72" t="s">
         <v>96</v>
@@ -15158,10 +15252,10 @@
         <v>83</v>
       </c>
       <c r="BL52" s="72" t="s">
+        <v>203</v>
+      </c>
+      <c r="BM52" s="72" t="s">
         <v>204</v>
-      </c>
-      <c r="BM52" s="72" t="s">
-        <v>205</v>
       </c>
       <c r="BN52" s="72" t="s">
         <v>119</v>
@@ -15233,7 +15327,7 @@
         <v>5.2722872763891163E-6</v>
       </c>
     </row>
-    <row r="53" spans="1:87" s="110" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:90" s="110" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="110" t="s">
         <v>115</v>
       </c>
@@ -15244,16 +15338,16 @@
         <v>523</v>
       </c>
       <c r="E53" s="110" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F53" s="110">
         <v>2025</v>
       </c>
       <c r="G53" s="110" t="s">
+        <v>210</v>
+      </c>
+      <c r="H53" s="110" t="s">
         <v>211</v>
-      </c>
-      <c r="H53" s="110" t="s">
-        <v>212</v>
       </c>
       <c r="I53" s="110">
         <v>2</v>
@@ -15267,7 +15361,7 @@
       <c r="BZ53" s="114"/>
       <c r="CA53" s="114"/>
     </row>
-    <row r="54" spans="1:87" s="72" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:90" s="72" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="91" t="s">
         <v>120</v>
       </c>
@@ -15279,29 +15373,29 @@
         <v>524</v>
       </c>
       <c r="E54" s="91" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F54" s="91">
         <v>2022</v>
       </c>
       <c r="G54" s="91" t="s">
+        <v>213</v>
+      </c>
+      <c r="H54" s="91" t="s">
         <v>214</v>
-      </c>
-      <c r="H54" s="91" t="s">
-        <v>215</v>
       </c>
       <c r="I54" s="91">
         <v>2</v>
       </c>
       <c r="J54" s="91" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K54" s="91" t="s">
         <v>83</v>
       </c>
       <c r="L54" s="91"/>
       <c r="M54" s="91" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N54" s="91" t="s">
         <v>85</v>
@@ -15334,73 +15428,73 @@
         <v>95</v>
       </c>
       <c r="X54" s="91" t="s">
+        <v>217</v>
+      </c>
+      <c r="Y54" s="91">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="91">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="91">
+        <v>0</v>
+      </c>
+      <c r="AB54" s="91">
+        <v>1</v>
+      </c>
+      <c r="AC54" s="91">
+        <v>0</v>
+      </c>
+      <c r="AD54" s="91">
+        <v>0</v>
+      </c>
+      <c r="AE54" s="91">
+        <v>0</v>
+      </c>
+      <c r="AF54" s="91">
+        <v>0</v>
+      </c>
+      <c r="AG54" s="91" t="s">
         <v>218</v>
       </c>
-      <c r="Y54" s="91">
-        <v>0</v>
-      </c>
-      <c r="Z54" s="91">
-        <v>0</v>
-      </c>
-      <c r="AA54" s="91">
-        <v>0</v>
-      </c>
-      <c r="AB54" s="91">
-        <v>1</v>
-      </c>
-      <c r="AC54" s="91">
-        <v>0</v>
-      </c>
-      <c r="AD54" s="91">
-        <v>0</v>
-      </c>
-      <c r="AE54" s="91">
-        <v>0</v>
-      </c>
-      <c r="AF54" s="91">
-        <v>0</v>
-      </c>
-      <c r="AG54" s="91" t="s">
+      <c r="AH54" s="91">
+        <v>0</v>
+      </c>
+      <c r="AI54" s="91">
+        <v>0</v>
+      </c>
+      <c r="AJ54" s="91">
+        <v>0</v>
+      </c>
+      <c r="AK54" s="91">
+        <v>0</v>
+      </c>
+      <c r="AL54" s="91">
+        <v>1</v>
+      </c>
+      <c r="AM54" s="91">
+        <v>0</v>
+      </c>
+      <c r="AN54" s="91">
+        <v>0</v>
+      </c>
+      <c r="AO54" s="91">
+        <v>0</v>
+      </c>
+      <c r="AP54" s="91">
+        <v>0</v>
+      </c>
+      <c r="AQ54" s="91" t="s">
+        <v>216</v>
+      </c>
+      <c r="AR54" s="91" t="s">
         <v>219</v>
       </c>
-      <c r="AH54" s="91">
-        <v>0</v>
-      </c>
-      <c r="AI54" s="91">
-        <v>0</v>
-      </c>
-      <c r="AJ54" s="91">
-        <v>0</v>
-      </c>
-      <c r="AK54" s="91">
-        <v>0</v>
-      </c>
-      <c r="AL54" s="91">
-        <v>1</v>
-      </c>
-      <c r="AM54" s="91">
-        <v>0</v>
-      </c>
-      <c r="AN54" s="91">
-        <v>0</v>
-      </c>
-      <c r="AO54" s="91">
-        <v>0</v>
-      </c>
-      <c r="AP54" s="91">
-        <v>0</v>
-      </c>
-      <c r="AQ54" s="91" t="s">
-        <v>217</v>
-      </c>
-      <c r="AR54" s="91" t="s">
+      <c r="AS54" s="91" t="s">
         <v>220</v>
       </c>
-      <c r="AS54" s="91" t="s">
-        <v>221</v>
-      </c>
       <c r="AT54" s="91" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AU54" s="91">
         <v>8.0000000000000002E-3</v>
@@ -15453,13 +15547,13 @@
         <v>83</v>
       </c>
       <c r="BL54" s="91" t="s">
+        <v>221</v>
+      </c>
+      <c r="BM54" s="91" t="s">
+        <v>83</v>
+      </c>
+      <c r="BN54" s="91" t="s">
         <v>222</v>
-      </c>
-      <c r="BM54" s="91" t="s">
-        <v>83</v>
-      </c>
-      <c r="BN54" s="91" t="s">
-        <v>223</v>
       </c>
       <c r="BO54" s="91" t="s">
         <v>83</v>
@@ -15528,7 +15622,7 @@
         <v>4.5266893604693271E-6</v>
       </c>
     </row>
-    <row r="55" spans="1:87" s="72" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:90" s="72" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="91" t="s">
         <v>120</v>
       </c>
@@ -15540,29 +15634,29 @@
         <v>524</v>
       </c>
       <c r="E55" s="91" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F55" s="91">
         <v>2022</v>
       </c>
       <c r="G55" s="91" t="s">
+        <v>213</v>
+      </c>
+      <c r="H55" s="91" t="s">
         <v>214</v>
-      </c>
-      <c r="H55" s="91" t="s">
-        <v>215</v>
       </c>
       <c r="I55" s="91">
         <v>2</v>
       </c>
       <c r="J55" s="91" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K55" s="91" t="s">
         <v>83</v>
       </c>
       <c r="L55" s="91"/>
       <c r="M55" s="91" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N55" s="91" t="s">
         <v>85</v>
@@ -15595,73 +15689,73 @@
         <v>95</v>
       </c>
       <c r="X55" s="91" t="s">
+        <v>217</v>
+      </c>
+      <c r="Y55" s="91">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="91">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="91">
+        <v>0</v>
+      </c>
+      <c r="AB55" s="91">
+        <v>1</v>
+      </c>
+      <c r="AC55" s="91">
+        <v>0</v>
+      </c>
+      <c r="AD55" s="91">
+        <v>0</v>
+      </c>
+      <c r="AE55" s="91">
+        <v>0</v>
+      </c>
+      <c r="AF55" s="91">
+        <v>0</v>
+      </c>
+      <c r="AG55" s="91" t="s">
         <v>218</v>
       </c>
-      <c r="Y55" s="91">
-        <v>0</v>
-      </c>
-      <c r="Z55" s="91">
-        <v>0</v>
-      </c>
-      <c r="AA55" s="91">
-        <v>0</v>
-      </c>
-      <c r="AB55" s="91">
-        <v>1</v>
-      </c>
-      <c r="AC55" s="91">
-        <v>0</v>
-      </c>
-      <c r="AD55" s="91">
-        <v>0</v>
-      </c>
-      <c r="AE55" s="91">
-        <v>0</v>
-      </c>
-      <c r="AF55" s="91">
-        <v>0</v>
-      </c>
-      <c r="AG55" s="91" t="s">
+      <c r="AH55" s="91">
+        <v>0</v>
+      </c>
+      <c r="AI55" s="91">
+        <v>0</v>
+      </c>
+      <c r="AJ55" s="91">
+        <v>0</v>
+      </c>
+      <c r="AK55" s="91">
+        <v>0</v>
+      </c>
+      <c r="AL55" s="91">
+        <v>1</v>
+      </c>
+      <c r="AM55" s="91">
+        <v>0</v>
+      </c>
+      <c r="AN55" s="91">
+        <v>0</v>
+      </c>
+      <c r="AO55" s="91">
+        <v>0</v>
+      </c>
+      <c r="AP55" s="91">
+        <v>0</v>
+      </c>
+      <c r="AQ55" s="91" t="s">
+        <v>216</v>
+      </c>
+      <c r="AR55" s="91" t="s">
         <v>219</v>
       </c>
-      <c r="AH55" s="91">
-        <v>0</v>
-      </c>
-      <c r="AI55" s="91">
-        <v>0</v>
-      </c>
-      <c r="AJ55" s="91">
-        <v>0</v>
-      </c>
-      <c r="AK55" s="91">
-        <v>0</v>
-      </c>
-      <c r="AL55" s="91">
-        <v>1</v>
-      </c>
-      <c r="AM55" s="91">
-        <v>0</v>
-      </c>
-      <c r="AN55" s="91">
-        <v>0</v>
-      </c>
-      <c r="AO55" s="91">
-        <v>0</v>
-      </c>
-      <c r="AP55" s="91">
-        <v>0</v>
-      </c>
-      <c r="AQ55" s="91" t="s">
-        <v>217</v>
-      </c>
-      <c r="AR55" s="91" t="s">
+      <c r="AS55" s="91" t="s">
         <v>220</v>
       </c>
-      <c r="AS55" s="91" t="s">
-        <v>221</v>
-      </c>
       <c r="AT55" s="91" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AU55" s="91">
         <v>1.2999999999999999E-2</v>
@@ -15714,13 +15808,13 @@
         <v>83</v>
       </c>
       <c r="BL55" s="91" t="s">
+        <v>221</v>
+      </c>
+      <c r="BM55" s="91" t="s">
+        <v>83</v>
+      </c>
+      <c r="BN55" s="91" t="s">
         <v>222</v>
-      </c>
-      <c r="BM55" s="91" t="s">
-        <v>83</v>
-      </c>
-      <c r="BN55" s="91" t="s">
-        <v>223</v>
       </c>
       <c r="BO55" s="91" t="s">
         <v>83</v>
@@ -15789,7 +15883,7 @@
         <v>4.5266893604693271E-6</v>
       </c>
     </row>
-    <row r="56" spans="1:87" s="72" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:90" s="72" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="91" t="s">
         <v>120</v>
       </c>
@@ -15801,29 +15895,29 @@
         <v>524</v>
       </c>
       <c r="E56" s="91" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F56" s="91">
         <v>2022</v>
       </c>
       <c r="G56" s="91" t="s">
+        <v>213</v>
+      </c>
+      <c r="H56" s="91" t="s">
         <v>214</v>
-      </c>
-      <c r="H56" s="91" t="s">
-        <v>215</v>
       </c>
       <c r="I56" s="91">
         <v>2</v>
       </c>
       <c r="J56" s="91" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K56" s="91" t="s">
         <v>83</v>
       </c>
       <c r="L56" s="91"/>
       <c r="M56" s="91" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N56" s="91" t="s">
         <v>85</v>
@@ -15856,73 +15950,73 @@
         <v>95</v>
       </c>
       <c r="X56" s="91" t="s">
+        <v>217</v>
+      </c>
+      <c r="Y56" s="91">
+        <v>0</v>
+      </c>
+      <c r="Z56" s="91">
+        <v>0</v>
+      </c>
+      <c r="AA56" s="91">
+        <v>0</v>
+      </c>
+      <c r="AB56" s="91">
+        <v>1</v>
+      </c>
+      <c r="AC56" s="91">
+        <v>0</v>
+      </c>
+      <c r="AD56" s="91">
+        <v>0</v>
+      </c>
+      <c r="AE56" s="91">
+        <v>0</v>
+      </c>
+      <c r="AF56" s="91">
+        <v>0</v>
+      </c>
+      <c r="AG56" s="91" t="s">
         <v>218</v>
       </c>
-      <c r="Y56" s="91">
-        <v>0</v>
-      </c>
-      <c r="Z56" s="91">
-        <v>0</v>
-      </c>
-      <c r="AA56" s="91">
-        <v>0</v>
-      </c>
-      <c r="AB56" s="91">
-        <v>1</v>
-      </c>
-      <c r="AC56" s="91">
-        <v>0</v>
-      </c>
-      <c r="AD56" s="91">
-        <v>0</v>
-      </c>
-      <c r="AE56" s="91">
-        <v>0</v>
-      </c>
-      <c r="AF56" s="91">
-        <v>0</v>
-      </c>
-      <c r="AG56" s="91" t="s">
+      <c r="AH56" s="91">
+        <v>0</v>
+      </c>
+      <c r="AI56" s="91">
+        <v>0</v>
+      </c>
+      <c r="AJ56" s="91">
+        <v>0</v>
+      </c>
+      <c r="AK56" s="91">
+        <v>0</v>
+      </c>
+      <c r="AL56" s="91">
+        <v>1</v>
+      </c>
+      <c r="AM56" s="91">
+        <v>0</v>
+      </c>
+      <c r="AN56" s="91">
+        <v>0</v>
+      </c>
+      <c r="AO56" s="91">
+        <v>0</v>
+      </c>
+      <c r="AP56" s="91">
+        <v>0</v>
+      </c>
+      <c r="AQ56" s="91" t="s">
+        <v>216</v>
+      </c>
+      <c r="AR56" s="91" t="s">
         <v>219</v>
       </c>
-      <c r="AH56" s="91">
-        <v>0</v>
-      </c>
-      <c r="AI56" s="91">
-        <v>0</v>
-      </c>
-      <c r="AJ56" s="91">
-        <v>0</v>
-      </c>
-      <c r="AK56" s="91">
-        <v>0</v>
-      </c>
-      <c r="AL56" s="91">
-        <v>1</v>
-      </c>
-      <c r="AM56" s="91">
-        <v>0</v>
-      </c>
-      <c r="AN56" s="91">
-        <v>0</v>
-      </c>
-      <c r="AO56" s="91">
-        <v>0</v>
-      </c>
-      <c r="AP56" s="91">
-        <v>0</v>
-      </c>
-      <c r="AQ56" s="91" t="s">
-        <v>217</v>
-      </c>
-      <c r="AR56" s="91" t="s">
+      <c r="AS56" s="91" t="s">
         <v>220</v>
       </c>
-      <c r="AS56" s="91" t="s">
-        <v>221</v>
-      </c>
       <c r="AT56" s="91" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AU56" s="91">
         <v>1.7000000000000001E-2</v>
@@ -15975,13 +16069,13 @@
         <v>83</v>
       </c>
       <c r="BL56" s="91" t="s">
+        <v>221</v>
+      </c>
+      <c r="BM56" s="91" t="s">
+        <v>83</v>
+      </c>
+      <c r="BN56" s="91" t="s">
         <v>222</v>
-      </c>
-      <c r="BM56" s="91" t="s">
-        <v>83</v>
-      </c>
-      <c r="BN56" s="91" t="s">
-        <v>223</v>
       </c>
       <c r="BO56" s="91" t="s">
         <v>83</v>
@@ -16050,7 +16144,7 @@
         <v>4.5266893604693271E-6</v>
       </c>
     </row>
-    <row r="57" spans="1:87" s="72" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:90" s="72" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="91" t="s">
         <v>120</v>
       </c>
@@ -16062,22 +16156,22 @@
         <v>524</v>
       </c>
       <c r="E57" s="91" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F57" s="91">
         <v>2022</v>
       </c>
       <c r="G57" s="91" t="s">
+        <v>213</v>
+      </c>
+      <c r="H57" s="91" t="s">
         <v>214</v>
-      </c>
-      <c r="H57" s="91" t="s">
-        <v>215</v>
       </c>
       <c r="I57" s="91">
         <v>2</v>
       </c>
       <c r="J57" s="91" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K57" s="91" t="s">
         <v>83</v>
@@ -16117,35 +16211,35 @@
         <v>95</v>
       </c>
       <c r="X57" s="91" t="s">
+        <v>217</v>
+      </c>
+      <c r="Y57" s="91">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="91">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="91">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="91">
+        <v>1</v>
+      </c>
+      <c r="AC57" s="91">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="91">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="91">
+        <v>0</v>
+      </c>
+      <c r="AF57" s="91">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="91" t="s">
         <v>218</v>
       </c>
-      <c r="Y57" s="91">
-        <v>0</v>
-      </c>
-      <c r="Z57" s="91">
-        <v>0</v>
-      </c>
-      <c r="AA57" s="91">
-        <v>0</v>
-      </c>
-      <c r="AB57" s="91">
-        <v>1</v>
-      </c>
-      <c r="AC57" s="91">
-        <v>0</v>
-      </c>
-      <c r="AD57" s="91">
-        <v>0</v>
-      </c>
-      <c r="AE57" s="91">
-        <v>0</v>
-      </c>
-      <c r="AF57" s="91">
-        <v>0</v>
-      </c>
-      <c r="AG57" s="91" t="s">
-        <v>219</v>
-      </c>
       <c r="AH57" s="91">
         <v>0</v>
       </c>
@@ -16174,13 +16268,13 @@
         <v>0</v>
       </c>
       <c r="AQ57" s="91" t="s">
+        <v>223</v>
+      </c>
+      <c r="AR57" s="91" t="s">
+        <v>83</v>
+      </c>
+      <c r="AS57" s="91" t="s">
         <v>224</v>
-      </c>
-      <c r="AR57" s="91" t="s">
-        <v>83</v>
-      </c>
-      <c r="AS57" s="91" t="s">
-        <v>225</v>
       </c>
       <c r="AT57" s="91" t="s">
         <v>83</v>
@@ -16236,13 +16330,13 @@
         <v>83</v>
       </c>
       <c r="BL57" s="91" t="s">
+        <v>221</v>
+      </c>
+      <c r="BM57" s="91" t="s">
+        <v>83</v>
+      </c>
+      <c r="BN57" s="91" t="s">
         <v>222</v>
-      </c>
-      <c r="BM57" s="91" t="s">
-        <v>83</v>
-      </c>
-      <c r="BN57" s="91" t="s">
-        <v>223</v>
       </c>
       <c r="BO57" s="91" t="s">
         <v>83</v>
@@ -16311,7 +16405,7 @@
         <v>4.4002464137991729E-5</v>
       </c>
     </row>
-    <row r="58" spans="1:87" s="72" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:90" s="72" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="91" t="s">
         <v>120</v>
       </c>
@@ -16323,22 +16417,22 @@
         <v>524</v>
       </c>
       <c r="E58" s="91" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F58" s="91">
         <v>2022</v>
       </c>
       <c r="G58" s="91" t="s">
+        <v>213</v>
+      </c>
+      <c r="H58" s="91" t="s">
         <v>214</v>
-      </c>
-      <c r="H58" s="91" t="s">
-        <v>215</v>
       </c>
       <c r="I58" s="91">
         <v>2</v>
       </c>
       <c r="J58" s="91" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K58" s="91" t="s">
         <v>83</v>
@@ -16378,35 +16472,35 @@
         <v>95</v>
       </c>
       <c r="X58" s="91" t="s">
+        <v>217</v>
+      </c>
+      <c r="Y58" s="91">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="91">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="91">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="91">
+        <v>1</v>
+      </c>
+      <c r="AC58" s="91">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="91">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="91">
+        <v>0</v>
+      </c>
+      <c r="AF58" s="91">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="91" t="s">
         <v>218</v>
       </c>
-      <c r="Y58" s="91">
-        <v>0</v>
-      </c>
-      <c r="Z58" s="91">
-        <v>0</v>
-      </c>
-      <c r="AA58" s="91">
-        <v>0</v>
-      </c>
-      <c r="AB58" s="91">
-        <v>1</v>
-      </c>
-      <c r="AC58" s="91">
-        <v>0</v>
-      </c>
-      <c r="AD58" s="91">
-        <v>0</v>
-      </c>
-      <c r="AE58" s="91">
-        <v>0</v>
-      </c>
-      <c r="AF58" s="91">
-        <v>0</v>
-      </c>
-      <c r="AG58" s="91" t="s">
-        <v>219</v>
-      </c>
       <c r="AH58" s="91">
         <v>0</v>
       </c>
@@ -16435,13 +16529,13 @@
         <v>0</v>
       </c>
       <c r="AQ58" s="91" t="s">
+        <v>223</v>
+      </c>
+      <c r="AR58" s="91" t="s">
+        <v>83</v>
+      </c>
+      <c r="AS58" s="91" t="s">
         <v>224</v>
-      </c>
-      <c r="AR58" s="91" t="s">
-        <v>83</v>
-      </c>
-      <c r="AS58" s="91" t="s">
-        <v>225</v>
       </c>
       <c r="AT58" s="91" t="s">
         <v>83</v>
@@ -16497,13 +16591,13 @@
         <v>83</v>
       </c>
       <c r="BL58" s="91" t="s">
+        <v>221</v>
+      </c>
+      <c r="BM58" s="91" t="s">
+        <v>83</v>
+      </c>
+      <c r="BN58" s="91" t="s">
         <v>222</v>
-      </c>
-      <c r="BM58" s="91" t="s">
-        <v>83</v>
-      </c>
-      <c r="BN58" s="91" t="s">
-        <v>223</v>
       </c>
       <c r="BO58" s="91" t="s">
         <v>83</v>
@@ -16574,7 +16668,7 @@
       <c r="CH58" s="92"/>
       <c r="CI58" s="92"/>
     </row>
-    <row r="59" spans="1:87" s="72" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:90" s="72" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="91" t="s">
         <v>120</v>
       </c>
@@ -16586,22 +16680,22 @@
         <v>524</v>
       </c>
       <c r="E59" s="91" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F59" s="91">
         <v>2022</v>
       </c>
       <c r="G59" s="91" t="s">
+        <v>213</v>
+      </c>
+      <c r="H59" s="91" t="s">
         <v>214</v>
-      </c>
-      <c r="H59" s="91" t="s">
-        <v>215</v>
       </c>
       <c r="I59" s="91">
         <v>2</v>
       </c>
       <c r="J59" s="91" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K59" s="91" t="s">
         <v>83</v>
@@ -16641,35 +16735,35 @@
         <v>95</v>
       </c>
       <c r="X59" s="91" t="s">
+        <v>217</v>
+      </c>
+      <c r="Y59" s="91">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="91">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="91">
+        <v>0</v>
+      </c>
+      <c r="AB59" s="91">
+        <v>1</v>
+      </c>
+      <c r="AC59" s="91">
+        <v>0</v>
+      </c>
+      <c r="AD59" s="91">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="91">
+        <v>0</v>
+      </c>
+      <c r="AF59" s="91">
+        <v>0</v>
+      </c>
+      <c r="AG59" s="91" t="s">
         <v>218</v>
       </c>
-      <c r="Y59" s="91">
-        <v>0</v>
-      </c>
-      <c r="Z59" s="91">
-        <v>0</v>
-      </c>
-      <c r="AA59" s="91">
-        <v>0</v>
-      </c>
-      <c r="AB59" s="91">
-        <v>1</v>
-      </c>
-      <c r="AC59" s="91">
-        <v>0</v>
-      </c>
-      <c r="AD59" s="91">
-        <v>0</v>
-      </c>
-      <c r="AE59" s="91">
-        <v>0</v>
-      </c>
-      <c r="AF59" s="91">
-        <v>0</v>
-      </c>
-      <c r="AG59" s="91" t="s">
-        <v>219</v>
-      </c>
       <c r="AH59" s="91">
         <v>0</v>
       </c>
@@ -16698,13 +16792,13 @@
         <v>0</v>
       </c>
       <c r="AQ59" s="91" t="s">
+        <v>223</v>
+      </c>
+      <c r="AR59" s="91" t="s">
+        <v>83</v>
+      </c>
+      <c r="AS59" s="91" t="s">
         <v>224</v>
-      </c>
-      <c r="AR59" s="91" t="s">
-        <v>83</v>
-      </c>
-      <c r="AS59" s="91" t="s">
-        <v>225</v>
       </c>
       <c r="AT59" s="91" t="s">
         <v>83</v>
@@ -16760,13 +16854,13 @@
         <v>83</v>
       </c>
       <c r="BL59" s="91" t="s">
+        <v>221</v>
+      </c>
+      <c r="BM59" s="91" t="s">
+        <v>83</v>
+      </c>
+      <c r="BN59" s="91" t="s">
         <v>222</v>
-      </c>
-      <c r="BM59" s="91" t="s">
-        <v>83</v>
-      </c>
-      <c r="BN59" s="91" t="s">
-        <v>223</v>
       </c>
       <c r="BO59" s="91" t="s">
         <v>83</v>
@@ -16837,374 +16931,3766 @@
       <c r="CH59" s="92"/>
       <c r="CI59" s="92"/>
     </row>
-    <row r="60" spans="1:87" x14ac:dyDescent="0.3">
-      <c r="A60" s="35"/>
-      <c r="B60" s="35"/>
-      <c r="C60" s="35"/>
-      <c r="D60" s="35"/>
-      <c r="F60" s="35"/>
-      <c r="H60" s="2"/>
-      <c r="I60" s="35"/>
-      <c r="P60" s="35"/>
-      <c r="V60" s="35"/>
-      <c r="W60" s="35"/>
-      <c r="X60" s="35"/>
-      <c r="AU60" s="40"/>
-      <c r="AV60" s="41"/>
-      <c r="BA60" s="44"/>
-      <c r="BF60" s="35"/>
-      <c r="BT60" s="35"/>
-      <c r="BU60" s="35"/>
-      <c r="BV60" s="35"/>
-      <c r="BW60" s="36"/>
-      <c r="BX60" s="36"/>
-      <c r="BY60" s="37"/>
-      <c r="BZ60" s="36"/>
-      <c r="CA60" s="38"/>
-      <c r="CF60" s="39"/>
-      <c r="CG60" s="39"/>
-      <c r="CH60" s="39"/>
-      <c r="CI60" s="39"/>
-    </row>
-    <row r="61" spans="1:87" x14ac:dyDescent="0.3">
-      <c r="A61" s="35"/>
-      <c r="B61" s="35"/>
-      <c r="C61" s="35"/>
-      <c r="D61" s="35"/>
-      <c r="F61" s="35"/>
-      <c r="H61" s="2"/>
-      <c r="I61" s="35"/>
-      <c r="P61" s="35"/>
-      <c r="V61" s="35"/>
-      <c r="W61" s="35"/>
-      <c r="X61" s="35"/>
-      <c r="AU61" s="40"/>
-      <c r="AV61" s="41"/>
-      <c r="BA61" s="44"/>
-      <c r="BF61" s="35"/>
-      <c r="BT61" s="35"/>
-      <c r="BU61" s="35"/>
-      <c r="BV61" s="35"/>
-      <c r="BW61" s="36"/>
-      <c r="BX61" s="36"/>
-      <c r="BY61" s="37"/>
-      <c r="BZ61" s="36"/>
-      <c r="CA61" s="38"/>
-      <c r="CF61" s="39"/>
-      <c r="CG61" s="39"/>
-      <c r="CH61" s="39"/>
-      <c r="CI61" s="39"/>
-    </row>
-    <row r="62" spans="1:87" x14ac:dyDescent="0.3">
-      <c r="A62" s="35"/>
-      <c r="B62" s="35"/>
-      <c r="C62" s="35"/>
-      <c r="D62" s="35"/>
-      <c r="F62" s="35"/>
-      <c r="H62" s="2"/>
-      <c r="I62" s="35"/>
-      <c r="P62" s="35"/>
-      <c r="V62" s="35"/>
-      <c r="W62" s="35"/>
-      <c r="X62" s="35"/>
-      <c r="AU62" s="40"/>
-      <c r="AV62" s="41"/>
-      <c r="BA62" s="62"/>
-      <c r="BF62" s="35"/>
-      <c r="BT62" s="35"/>
-      <c r="BU62" s="35"/>
-      <c r="BV62" s="35"/>
-      <c r="BW62" s="36"/>
-      <c r="BX62" s="36"/>
-      <c r="BY62" s="37"/>
-      <c r="BZ62" s="36"/>
-      <c r="CA62" s="38"/>
-      <c r="CF62" s="39"/>
-      <c r="CG62" s="39"/>
-      <c r="CH62" s="39"/>
-      <c r="CI62" s="39"/>
-    </row>
-    <row r="63" spans="1:87" x14ac:dyDescent="0.3">
-      <c r="A63" s="35"/>
-      <c r="B63" s="35"/>
-      <c r="C63" s="35"/>
-      <c r="D63" s="35"/>
-      <c r="F63" s="35"/>
-      <c r="H63" s="2"/>
-      <c r="I63" s="35"/>
-      <c r="P63" s="35"/>
-      <c r="V63" s="35"/>
-      <c r="W63" s="35"/>
-      <c r="X63" s="35"/>
-      <c r="AU63" s="40"/>
-      <c r="AV63" s="41"/>
-      <c r="BA63" s="62"/>
-      <c r="BF63" s="35"/>
-      <c r="BT63" s="35"/>
-      <c r="BU63" s="35"/>
-      <c r="BV63" s="35"/>
-      <c r="BW63" s="36"/>
-      <c r="BX63" s="36"/>
-      <c r="BY63" s="37"/>
-      <c r="BZ63" s="36"/>
-      <c r="CA63" s="38"/>
-      <c r="CF63" s="39"/>
-      <c r="CG63" s="39"/>
-      <c r="CH63" s="39"/>
-      <c r="CI63" s="39"/>
-    </row>
-    <row r="64" spans="1:87" x14ac:dyDescent="0.3">
-      <c r="A64" s="35"/>
-      <c r="B64" s="35"/>
-      <c r="C64" s="35"/>
-      <c r="D64" s="35"/>
-      <c r="F64" s="35"/>
-      <c r="H64" s="2"/>
-      <c r="I64" s="35"/>
-      <c r="P64" s="35"/>
-      <c r="V64" s="35"/>
-      <c r="W64" s="35"/>
-      <c r="X64" s="35"/>
-      <c r="AU64" s="40"/>
-      <c r="AV64" s="41"/>
-      <c r="BA64" s="62"/>
-      <c r="BF64" s="35"/>
-      <c r="BT64" s="35"/>
-      <c r="BU64" s="35"/>
-      <c r="BV64" s="35"/>
-      <c r="BW64" s="36"/>
-      <c r="BX64" s="36"/>
-      <c r="BY64" s="37"/>
-      <c r="BZ64" s="36"/>
-      <c r="CA64" s="38"/>
-      <c r="CF64" s="39"/>
-      <c r="CG64" s="39"/>
-      <c r="CH64" s="39"/>
-      <c r="CI64" s="39"/>
-    </row>
-    <row r="65" spans="1:87" x14ac:dyDescent="0.3">
-      <c r="A65" s="35"/>
+    <row r="60" spans="1:90" s="115" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A60" s="72" t="s">
+        <v>107</v>
+      </c>
+      <c r="B60" s="72"/>
+      <c r="C60" s="35">
+        <v>1538</v>
+      </c>
+      <c r="D60" s="72">
+        <v>511</v>
+      </c>
+      <c r="E60" s="72" t="s">
+        <v>492</v>
+      </c>
+      <c r="F60" s="72">
+        <v>2023</v>
+      </c>
+      <c r="G60" s="72" t="s">
+        <v>491</v>
+      </c>
+      <c r="H60" s="72" t="s">
+        <v>490</v>
+      </c>
+      <c r="I60" s="72">
+        <v>1</v>
+      </c>
+      <c r="J60" s="72" t="s">
+        <v>489</v>
+      </c>
+      <c r="K60" s="72"/>
+      <c r="L60" s="72">
+        <v>12</v>
+      </c>
+      <c r="M60" s="72" t="s">
+        <v>488</v>
+      </c>
+      <c r="N60" s="72" t="s">
+        <v>93</v>
+      </c>
+      <c r="O60" s="72" t="s">
+        <v>94</v>
+      </c>
+      <c r="P60" s="72" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q60" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="R60" s="72" t="s">
+        <v>109</v>
+      </c>
+      <c r="S60" s="72">
+        <v>0</v>
+      </c>
+      <c r="T60" s="72" t="s">
+        <v>110</v>
+      </c>
+      <c r="U60" s="72">
+        <v>0</v>
+      </c>
+      <c r="V60" s="72" t="s">
+        <v>90</v>
+      </c>
+      <c r="W60" s="72" t="s">
+        <v>95</v>
+      </c>
+      <c r="X60" s="72" t="s">
+        <v>498</v>
+      </c>
+      <c r="Y60" s="72">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="72">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="72">
+        <v>1</v>
+      </c>
+      <c r="AB60" s="72">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="72">
+        <v>0</v>
+      </c>
+      <c r="AD60" s="72">
+        <v>0</v>
+      </c>
+      <c r="AE60" s="72">
+        <v>0</v>
+      </c>
+      <c r="AF60" s="72">
+        <v>0</v>
+      </c>
+      <c r="AG60" s="72" t="s">
+        <v>499</v>
+      </c>
+      <c r="AH60" s="72">
+        <v>0</v>
+      </c>
+      <c r="AI60" s="72">
+        <v>0</v>
+      </c>
+      <c r="AJ60" s="72">
+        <v>0</v>
+      </c>
+      <c r="AK60" s="72">
+        <v>1</v>
+      </c>
+      <c r="AL60" s="72">
+        <v>0</v>
+      </c>
+      <c r="AM60" s="72">
+        <v>0</v>
+      </c>
+      <c r="AN60" s="72">
+        <v>0</v>
+      </c>
+      <c r="AO60" s="72">
+        <v>0</v>
+      </c>
+      <c r="AP60" s="72">
+        <v>0</v>
+      </c>
+      <c r="AQ60" s="72" t="s">
+        <v>485</v>
+      </c>
+      <c r="AR60" s="72" t="s">
+        <v>105</v>
+      </c>
+      <c r="AS60" s="72" t="s">
+        <v>484</v>
+      </c>
+      <c r="AT60" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU60" s="73">
+        <v>0.44979999999999998</v>
+      </c>
+      <c r="AV60" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="AW60" s="72">
+        <v>1.3100000000000001E-2</v>
+      </c>
+      <c r="AX60" s="72">
+        <v>0.01</v>
+      </c>
+      <c r="AY60" s="72">
+        <v>1</v>
+      </c>
+      <c r="AZ60" s="72">
+        <f>AU60/AW60</f>
+        <v>34.335877862595417</v>
+      </c>
+      <c r="BA60" s="72"/>
+      <c r="BB60" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BC60" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BD60" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BE60" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BF60" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BG60" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BH60" s="72">
+        <v>1770</v>
+      </c>
+      <c r="BI60" s="72">
+        <v>1770</v>
+      </c>
+      <c r="BJ60" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BK60" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BL60" s="72">
+        <v>0</v>
+      </c>
+      <c r="BM60" s="72">
+        <v>0</v>
+      </c>
+      <c r="BN60" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BO60" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BP60" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BQ60" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BR60" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BS60" s="72" t="s">
+        <v>111</v>
+      </c>
+      <c r="BT60" s="72">
+        <v>0</v>
+      </c>
+      <c r="BU60" s="72">
+        <v>0</v>
+      </c>
+      <c r="BV60" s="72">
+        <v>1</v>
+      </c>
+      <c r="BW60" s="92">
+        <f>((AZ60^2)/(AZ60^2+BH60))^(1/2)</f>
+        <v>0.63228701965480538</v>
+      </c>
+      <c r="BX60" s="92">
+        <f>0.5*LN((1+BW60)/(1-BW60))</f>
+        <v>0.74521735040380777</v>
+      </c>
+      <c r="BY60" s="92">
+        <f>((1-(BX60^2)^2)/(BH60-1))</f>
+        <v>3.909483323904246E-4</v>
+      </c>
+      <c r="BZ60" s="92">
+        <f>1/(BH60-3)</f>
+        <v>5.6593095642331638E-4</v>
+      </c>
+      <c r="CA60" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="CB60" s="72">
+        <f>BH60-2</f>
+        <v>1768</v>
+      </c>
+      <c r="CC60" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="CD60" s="92">
+        <f>((AZ60^2)/(AZ60^2+BI60))^(1/2)</f>
+        <v>0.63228701965480538</v>
+      </c>
+      <c r="CE60" s="92">
+        <f>0.5*LN((1+CD60)/(1-CD60))</f>
+        <v>0.74521735040380777</v>
+      </c>
+      <c r="CF60" s="92">
+        <f>((1-(CE60^2)^2)/(BI60-1))</f>
+        <v>3.909483323904246E-4</v>
+      </c>
+      <c r="CG60" s="92">
+        <f>1/(BI60-3)</f>
+        <v>5.6593095642331638E-4</v>
+      </c>
+      <c r="CH60" s="72"/>
+      <c r="CI60" s="72"/>
+      <c r="CJ60" s="72"/>
+      <c r="CK60" s="72"/>
+      <c r="CL60" s="72"/>
+    </row>
+    <row r="61" spans="1:90" s="115" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A61" s="72" t="s">
+        <v>107</v>
+      </c>
+      <c r="B61" s="72"/>
+      <c r="C61" s="35">
+        <v>1539</v>
+      </c>
+      <c r="D61" s="72">
+        <v>511</v>
+      </c>
+      <c r="E61" s="72" t="s">
+        <v>492</v>
+      </c>
+      <c r="F61" s="72">
+        <v>2023</v>
+      </c>
+      <c r="G61" s="72" t="s">
+        <v>491</v>
+      </c>
+      <c r="H61" s="72" t="s">
+        <v>490</v>
+      </c>
+      <c r="I61" s="72">
+        <v>1</v>
+      </c>
+      <c r="J61" s="72" t="s">
+        <v>489</v>
+      </c>
+      <c r="K61" s="72"/>
+      <c r="L61" s="72">
+        <v>12</v>
+      </c>
+      <c r="M61" s="72" t="s">
+        <v>488</v>
+      </c>
+      <c r="N61" s="72" t="s">
+        <v>93</v>
+      </c>
+      <c r="O61" s="72" t="s">
+        <v>94</v>
+      </c>
+      <c r="P61" s="72" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q61" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="R61" s="72" t="s">
+        <v>109</v>
+      </c>
+      <c r="S61" s="72">
+        <v>0</v>
+      </c>
+      <c r="T61" s="72" t="s">
+        <v>110</v>
+      </c>
+      <c r="U61" s="72">
+        <v>0</v>
+      </c>
+      <c r="V61" s="72" t="s">
+        <v>90</v>
+      </c>
+      <c r="W61" s="72" t="s">
+        <v>95</v>
+      </c>
+      <c r="X61" s="72" t="s">
+        <v>498</v>
+      </c>
+      <c r="Y61" s="72">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="72">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="72">
+        <v>1</v>
+      </c>
+      <c r="AB61" s="72">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="72">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="72">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="72">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="72">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="72" t="s">
+        <v>497</v>
+      </c>
+      <c r="AH61" s="72">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="72">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="72">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="72">
+        <v>1</v>
+      </c>
+      <c r="AL61" s="72">
+        <v>0</v>
+      </c>
+      <c r="AM61" s="72">
+        <v>0</v>
+      </c>
+      <c r="AN61" s="72">
+        <v>0</v>
+      </c>
+      <c r="AO61" s="72">
+        <v>0</v>
+      </c>
+      <c r="AP61" s="72">
+        <v>0</v>
+      </c>
+      <c r="AQ61" s="72" t="s">
+        <v>485</v>
+      </c>
+      <c r="AR61" s="72" t="s">
+        <v>105</v>
+      </c>
+      <c r="AS61" s="72" t="s">
+        <v>484</v>
+      </c>
+      <c r="AT61" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU61" s="73">
+        <v>0.46029999999999999</v>
+      </c>
+      <c r="AV61" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="AW61" s="72">
+        <v>1.09E-2</v>
+      </c>
+      <c r="AX61" s="72">
+        <v>0.01</v>
+      </c>
+      <c r="AY61" s="72">
+        <v>1</v>
+      </c>
+      <c r="AZ61" s="72">
+        <f>AU61/AW61</f>
+        <v>42.22935779816514</v>
+      </c>
+      <c r="BA61" s="72"/>
+      <c r="BB61" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BC61" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BD61" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BE61" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BF61" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BG61" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BH61" s="72">
+        <v>1770</v>
+      </c>
+      <c r="BI61" s="72">
+        <v>1770</v>
+      </c>
+      <c r="BJ61" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BK61" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BL61" s="72">
+        <v>0</v>
+      </c>
+      <c r="BM61" s="72">
+        <v>0</v>
+      </c>
+      <c r="BN61" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BO61" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BP61" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BQ61" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BR61" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BS61" s="72" t="s">
+        <v>111</v>
+      </c>
+      <c r="BT61" s="72">
+        <v>0</v>
+      </c>
+      <c r="BU61" s="72">
+        <v>0</v>
+      </c>
+      <c r="BV61" s="72">
+        <v>1</v>
+      </c>
+      <c r="BW61" s="92">
+        <f>((AZ61^2)/(AZ61^2+BH61))^(1/2)</f>
+        <v>0.70843074158690655</v>
+      </c>
+      <c r="BX61" s="92">
+        <f>0.5*LN((1+BW61)/(1-BW61))</f>
+        <v>0.88402648121242355</v>
+      </c>
+      <c r="BY61" s="92">
+        <f>((1-(BX61^2)^2)/(BH61-1))</f>
+        <v>2.2004146022457753E-4</v>
+      </c>
+      <c r="BZ61" s="92">
+        <f>1/(BH61-3)</f>
+        <v>5.6593095642331638E-4</v>
+      </c>
+      <c r="CA61" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="CB61" s="72">
+        <f>BH61-2</f>
+        <v>1768</v>
+      </c>
+      <c r="CC61" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="CD61" s="92">
+        <f>((AZ61^2)/(AZ61^2+BI61))^(1/2)</f>
+        <v>0.70843074158690655</v>
+      </c>
+      <c r="CE61" s="92">
+        <f>0.5*LN((1+CD61)/(1-CD61))</f>
+        <v>0.88402648121242355</v>
+      </c>
+      <c r="CF61" s="92">
+        <f>((1-(CE61^2)^2)/(BI61-1))</f>
+        <v>2.2004146022457753E-4</v>
+      </c>
+      <c r="CG61" s="92">
+        <f>1/(BI61-3)</f>
+        <v>5.6593095642331638E-4</v>
+      </c>
+      <c r="CH61" s="72"/>
+      <c r="CI61" s="72"/>
+      <c r="CJ61" s="72"/>
+      <c r="CK61" s="72"/>
+      <c r="CL61" s="72"/>
+    </row>
+    <row r="62" spans="1:90" s="115" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A62" s="72" t="s">
+        <v>107</v>
+      </c>
+      <c r="B62" s="72"/>
+      <c r="C62" s="35">
+        <v>1540</v>
+      </c>
+      <c r="D62" s="72">
+        <v>511</v>
+      </c>
+      <c r="E62" s="72" t="s">
+        <v>492</v>
+      </c>
+      <c r="F62" s="72">
+        <v>2023</v>
+      </c>
+      <c r="G62" s="72" t="s">
+        <v>491</v>
+      </c>
+      <c r="H62" s="72" t="s">
+        <v>490</v>
+      </c>
+      <c r="I62" s="72">
+        <v>1</v>
+      </c>
+      <c r="J62" s="72" t="s">
+        <v>489</v>
+      </c>
+      <c r="K62" s="72"/>
+      <c r="L62" s="72">
+        <v>12</v>
+      </c>
+      <c r="M62" s="72" t="s">
+        <v>488</v>
+      </c>
+      <c r="N62" s="72" t="s">
+        <v>93</v>
+      </c>
+      <c r="O62" s="72" t="s">
+        <v>94</v>
+      </c>
+      <c r="P62" s="72" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q62" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="R62" s="72" t="s">
+        <v>109</v>
+      </c>
+      <c r="S62" s="72">
+        <v>0</v>
+      </c>
+      <c r="T62" s="72" t="s">
+        <v>110</v>
+      </c>
+      <c r="U62" s="72">
+        <v>0</v>
+      </c>
+      <c r="V62" s="72" t="s">
+        <v>90</v>
+      </c>
+      <c r="W62" s="72" t="s">
+        <v>95</v>
+      </c>
+      <c r="X62" s="72" t="s">
+        <v>487</v>
+      </c>
+      <c r="Y62" s="72">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="72">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="72">
+        <v>0</v>
+      </c>
+      <c r="AB62" s="72">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="72">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="72">
+        <v>1</v>
+      </c>
+      <c r="AE62" s="72">
+        <v>0</v>
+      </c>
+      <c r="AF62" s="72">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="72" t="s">
+        <v>496</v>
+      </c>
+      <c r="AH62" s="72">
+        <v>0</v>
+      </c>
+      <c r="AI62" s="72">
+        <v>0</v>
+      </c>
+      <c r="AJ62" s="72">
+        <v>0</v>
+      </c>
+      <c r="AK62" s="72">
+        <v>1</v>
+      </c>
+      <c r="AL62" s="72">
+        <v>0</v>
+      </c>
+      <c r="AM62" s="72">
+        <v>0</v>
+      </c>
+      <c r="AN62" s="72">
+        <v>0</v>
+      </c>
+      <c r="AO62" s="72">
+        <v>0</v>
+      </c>
+      <c r="AP62" s="72">
+        <v>0</v>
+      </c>
+      <c r="AQ62" s="72" t="s">
+        <v>485</v>
+      </c>
+      <c r="AR62" s="72" t="s">
+        <v>105</v>
+      </c>
+      <c r="AS62" s="72" t="s">
+        <v>484</v>
+      </c>
+      <c r="AT62" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU62" s="73">
+        <v>0.1668</v>
+      </c>
+      <c r="AV62" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="AW62" s="72">
+        <v>3.4200000000000001E-2</v>
+      </c>
+      <c r="AX62" s="72">
+        <v>0.01</v>
+      </c>
+      <c r="AY62" s="72">
+        <v>1</v>
+      </c>
+      <c r="AZ62" s="72">
+        <f>AU62/AW62</f>
+        <v>4.8771929824561404</v>
+      </c>
+      <c r="BA62" s="72"/>
+      <c r="BB62" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BC62" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BD62" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BE62" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BF62" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BG62" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BH62" s="72">
+        <v>1770</v>
+      </c>
+      <c r="BI62" s="72">
+        <v>1770</v>
+      </c>
+      <c r="BJ62" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BK62" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BL62" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BM62" s="72" t="s">
+        <v>495</v>
+      </c>
+      <c r="BN62" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BO62" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BP62" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BQ62" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BR62" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BS62" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BT62" s="72">
+        <v>0</v>
+      </c>
+      <c r="BU62" s="72">
+        <v>0</v>
+      </c>
+      <c r="BV62" s="72">
+        <v>1</v>
+      </c>
+      <c r="BW62" s="92">
+        <f>((AZ62^2)/(AZ62^2+BH62))^(1/2)</f>
+        <v>0.11515545157885519</v>
+      </c>
+      <c r="BX62" s="92">
+        <f>0.5*LN((1+BW62)/(1-BW62))</f>
+        <v>0.11566855727743759</v>
+      </c>
+      <c r="BY62" s="92">
+        <f>((1-(BX62^2)^2)/(BH62-1))</f>
+        <v>5.651899358972113E-4</v>
+      </c>
+      <c r="BZ62" s="92">
+        <f>1/(BH62-3)</f>
+        <v>5.6593095642331638E-4</v>
+      </c>
+      <c r="CA62" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="CB62" s="72">
+        <f>BH62-2</f>
+        <v>1768</v>
+      </c>
+      <c r="CC62" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="CD62" s="92">
+        <f>((AZ62^2)/(AZ62^2+BI62))^(1/2)</f>
+        <v>0.11515545157885519</v>
+      </c>
+      <c r="CE62" s="92">
+        <f>0.5*LN((1+CD62)/(1-CD62))</f>
+        <v>0.11566855727743759</v>
+      </c>
+      <c r="CF62" s="92">
+        <f>((1-(CE62^2)^2)/(BI62-1))</f>
+        <v>5.651899358972113E-4</v>
+      </c>
+      <c r="CG62" s="92">
+        <f>1/(BI62-3)</f>
+        <v>5.6593095642331638E-4</v>
+      </c>
+      <c r="CH62" s="72"/>
+      <c r="CI62" s="72"/>
+      <c r="CJ62" s="72"/>
+      <c r="CK62" s="72"/>
+      <c r="CL62" s="72"/>
+    </row>
+    <row r="63" spans="1:90" s="115" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A63" s="72" t="s">
+        <v>107</v>
+      </c>
+      <c r="B63" s="72"/>
+      <c r="C63" s="35">
+        <v>1541</v>
+      </c>
+      <c r="D63" s="72">
+        <v>511</v>
+      </c>
+      <c r="E63" s="72" t="s">
+        <v>492</v>
+      </c>
+      <c r="F63" s="72">
+        <v>2023</v>
+      </c>
+      <c r="G63" s="72" t="s">
+        <v>491</v>
+      </c>
+      <c r="H63" s="72" t="s">
+        <v>490</v>
+      </c>
+      <c r="I63" s="72">
+        <v>1</v>
+      </c>
+      <c r="J63" s="72" t="s">
+        <v>489</v>
+      </c>
+      <c r="K63" s="72"/>
+      <c r="L63" s="72">
+        <v>12</v>
+      </c>
+      <c r="M63" s="72" t="s">
+        <v>488</v>
+      </c>
+      <c r="N63" s="72" t="s">
+        <v>93</v>
+      </c>
+      <c r="O63" s="72" t="s">
+        <v>94</v>
+      </c>
+      <c r="P63" s="72" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q63" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="R63" s="72" t="s">
+        <v>109</v>
+      </c>
+      <c r="S63" s="72">
+        <v>0</v>
+      </c>
+      <c r="T63" s="72" t="s">
+        <v>110</v>
+      </c>
+      <c r="U63" s="72">
+        <v>0</v>
+      </c>
+      <c r="V63" s="72" t="s">
+        <v>90</v>
+      </c>
+      <c r="W63" s="72" t="s">
+        <v>95</v>
+      </c>
+      <c r="X63" s="72" t="s">
+        <v>487</v>
+      </c>
+      <c r="Y63" s="72">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="72">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="72">
+        <v>0</v>
+      </c>
+      <c r="AB63" s="72">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="72">
+        <v>0</v>
+      </c>
+      <c r="AD63" s="72">
+        <v>1</v>
+      </c>
+      <c r="AE63" s="72">
+        <v>0</v>
+      </c>
+      <c r="AF63" s="72">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="72" t="s">
+        <v>494</v>
+      </c>
+      <c r="AH63" s="72">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="72">
+        <v>0</v>
+      </c>
+      <c r="AJ63" s="72">
+        <v>0</v>
+      </c>
+      <c r="AK63" s="72">
+        <v>1</v>
+      </c>
+      <c r="AL63" s="72">
+        <v>0</v>
+      </c>
+      <c r="AM63" s="72">
+        <v>0</v>
+      </c>
+      <c r="AN63" s="72">
+        <v>0</v>
+      </c>
+      <c r="AO63" s="72">
+        <v>0</v>
+      </c>
+      <c r="AP63" s="72">
+        <v>0</v>
+      </c>
+      <c r="AQ63" s="72" t="s">
+        <v>485</v>
+      </c>
+      <c r="AR63" s="72" t="s">
+        <v>105</v>
+      </c>
+      <c r="AS63" s="72" t="s">
+        <v>484</v>
+      </c>
+      <c r="AT63" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU63" s="73">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="AV63" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="AW63" s="72">
+        <v>5.6300000000000003E-2</v>
+      </c>
+      <c r="AX63" s="72">
+        <v>0.1</v>
+      </c>
+      <c r="AY63" s="72">
+        <v>2</v>
+      </c>
+      <c r="AZ63" s="72">
+        <f>AU63/AW63</f>
+        <v>3.0195381882770867E-2</v>
+      </c>
+      <c r="BA63" s="72"/>
+      <c r="BB63" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BC63" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BD63" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BE63" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BF63" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BG63" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BH63" s="72">
+        <v>1770</v>
+      </c>
+      <c r="BI63" s="72">
+        <v>1770</v>
+      </c>
+      <c r="BJ63" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BK63" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BL63" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BM63" s="72" t="s">
+        <v>493</v>
+      </c>
+      <c r="BN63" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BO63" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BP63" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BQ63" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BR63" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BS63" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BT63" s="72">
+        <v>0</v>
+      </c>
+      <c r="BU63" s="72">
+        <v>0</v>
+      </c>
+      <c r="BV63" s="72">
+        <v>1</v>
+      </c>
+      <c r="BW63" s="92">
+        <f>((AZ63^2)/(AZ63^2+BH63))^(1/2)</f>
+        <v>7.1771790619335472E-4</v>
+      </c>
+      <c r="BX63" s="92">
+        <f>0.5*LN((1+BW63)/(1-BW63))</f>
+        <v>7.1771802943018388E-4</v>
+      </c>
+      <c r="BY63" s="92">
+        <f>((1-(BX63^2)^2)/(BH63-1))</f>
+        <v>5.6529112492918862E-4</v>
+      </c>
+      <c r="BZ63" s="92">
+        <f>1/(BH63-3)</f>
+        <v>5.6593095642331638E-4</v>
+      </c>
+      <c r="CA63" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="CB63" s="72">
+        <f>BH63-2</f>
+        <v>1768</v>
+      </c>
+      <c r="CC63" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="CD63" s="92">
+        <f>((AZ63^2)/(AZ63^2+BI63))^(1/2)</f>
+        <v>7.1771790619335472E-4</v>
+      </c>
+      <c r="CE63" s="92">
+        <f>0.5*LN((1+CD63)/(1-CD63))</f>
+        <v>7.1771802943018388E-4</v>
+      </c>
+      <c r="CF63" s="92">
+        <f>((1-(CE63^2)^2)/(BI63-1))</f>
+        <v>5.6529112492918862E-4</v>
+      </c>
+      <c r="CG63" s="92">
+        <f>1/(BI63-3)</f>
+        <v>5.6593095642331638E-4</v>
+      </c>
+      <c r="CH63" s="72"/>
+      <c r="CI63" s="72"/>
+      <c r="CJ63" s="72"/>
+      <c r="CK63" s="72"/>
+      <c r="CL63" s="72"/>
+    </row>
+    <row r="64" spans="1:90" s="115" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A64" s="72" t="s">
+        <v>107</v>
+      </c>
+      <c r="B64" s="72"/>
+      <c r="C64" s="35">
+        <v>1542</v>
+      </c>
+      <c r="D64" s="72">
+        <v>511</v>
+      </c>
+      <c r="E64" s="72" t="s">
+        <v>492</v>
+      </c>
+      <c r="F64" s="72">
+        <v>2023</v>
+      </c>
+      <c r="G64" s="72" t="s">
+        <v>491</v>
+      </c>
+      <c r="H64" s="72" t="s">
+        <v>490</v>
+      </c>
+      <c r="I64" s="72">
+        <v>1</v>
+      </c>
+      <c r="J64" s="72" t="s">
+        <v>489</v>
+      </c>
+      <c r="K64" s="72"/>
+      <c r="L64" s="72">
+        <v>12</v>
+      </c>
+      <c r="M64" s="72" t="s">
+        <v>488</v>
+      </c>
+      <c r="N64" s="72" t="s">
+        <v>93</v>
+      </c>
+      <c r="O64" s="72" t="s">
+        <v>94</v>
+      </c>
+      <c r="P64" s="72" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q64" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="R64" s="72" t="s">
+        <v>109</v>
+      </c>
+      <c r="S64" s="72">
+        <v>0</v>
+      </c>
+      <c r="T64" s="72" t="s">
+        <v>110</v>
+      </c>
+      <c r="U64" s="72">
+        <v>0</v>
+      </c>
+      <c r="V64" s="72" t="s">
+        <v>90</v>
+      </c>
+      <c r="W64" s="72" t="s">
+        <v>95</v>
+      </c>
+      <c r="X64" s="72" t="s">
+        <v>487</v>
+      </c>
+      <c r="Y64" s="72">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="72">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="72">
+        <v>0</v>
+      </c>
+      <c r="AB64" s="72">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="72">
+        <v>0</v>
+      </c>
+      <c r="AD64" s="72">
+        <v>1</v>
+      </c>
+      <c r="AE64" s="72">
+        <v>0</v>
+      </c>
+      <c r="AF64" s="72">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="72" t="s">
+        <v>486</v>
+      </c>
+      <c r="AH64" s="72">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="72">
+        <v>0</v>
+      </c>
+      <c r="AJ64" s="72">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="72">
+        <v>1</v>
+      </c>
+      <c r="AL64" s="72">
+        <v>0</v>
+      </c>
+      <c r="AM64" s="72">
+        <v>0</v>
+      </c>
+      <c r="AN64" s="72">
+        <v>0</v>
+      </c>
+      <c r="AO64" s="72">
+        <v>0</v>
+      </c>
+      <c r="AP64" s="72">
+        <v>0</v>
+      </c>
+      <c r="AQ64" s="72" t="s">
+        <v>485</v>
+      </c>
+      <c r="AR64" s="72" t="s">
+        <v>105</v>
+      </c>
+      <c r="AS64" s="72" t="s">
+        <v>484</v>
+      </c>
+      <c r="AT64" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU64" s="73">
+        <v>0.19209999999999999</v>
+      </c>
+      <c r="AV64" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="AW64" s="72">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="AX64" s="72">
+        <v>0.01</v>
+      </c>
+      <c r="AY64" s="72">
+        <v>1</v>
+      </c>
+      <c r="AZ64" s="72">
+        <v>17</v>
+      </c>
+      <c r="BA64" s="72"/>
+      <c r="BB64" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BC64" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BD64" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BE64" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BF64" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BG64" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BH64" s="72">
+        <v>1770</v>
+      </c>
+      <c r="BI64" s="72">
+        <v>1770</v>
+      </c>
+      <c r="BJ64" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BK64" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BL64" s="72" t="s">
+        <v>483</v>
+      </c>
+      <c r="BM64" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BN64" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BO64" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BP64" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BQ64" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BR64" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BS64" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="BT64" s="72">
+        <v>0</v>
+      </c>
+      <c r="BU64" s="72">
+        <v>0</v>
+      </c>
+      <c r="BV64" s="72">
+        <v>1</v>
+      </c>
+      <c r="BW64" s="92">
+        <f>((AZ64^2)/(AZ64^2+BH64))^(1/2)</f>
+        <v>0.37464569631307093</v>
+      </c>
+      <c r="BX64" s="92">
+        <f>0.5*LN((1+BW64)/(1-BW64))</f>
+        <v>0.39381646323580399</v>
+      </c>
+      <c r="BY64" s="92">
+        <f>((1-(BX64^2)^2)/(BH64-1))</f>
+        <v>5.5169398279422807E-4</v>
+      </c>
+      <c r="BZ64" s="92">
+        <f>1/(BH64-3)</f>
+        <v>5.6593095642331638E-4</v>
+      </c>
+      <c r="CA64" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="CB64" s="72">
+        <f>BH64-2</f>
+        <v>1768</v>
+      </c>
+      <c r="CC64" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="CD64" s="92">
+        <f>((AZ64^2)/(AZ64^2+BI64))^(1/2)</f>
+        <v>0.37464569631307093</v>
+      </c>
+      <c r="CE64" s="92">
+        <f>0.5*LN((1+CD64)/(1-CD64))</f>
+        <v>0.39381646323580399</v>
+      </c>
+      <c r="CF64" s="92">
+        <f>((1-(CE64^2)^2)/(BI64-1))</f>
+        <v>5.5169398279422807E-4</v>
+      </c>
+      <c r="CG64" s="92">
+        <f>1/(BI64-3)</f>
+        <v>5.6593095642331638E-4</v>
+      </c>
+      <c r="CH64" s="72"/>
+      <c r="CI64" s="72"/>
+      <c r="CJ64" s="72"/>
+      <c r="CK64" s="72"/>
+      <c r="CL64" s="72"/>
+    </row>
+    <row r="65" spans="1:90" s="115" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="35" t="s">
+        <v>80</v>
+      </c>
       <c r="B65" s="35"/>
-      <c r="C65" s="35"/>
-      <c r="D65" s="35"/>
-      <c r="F65" s="35"/>
-      <c r="H65" s="2"/>
-      <c r="I65" s="35"/>
-      <c r="P65" s="35"/>
-      <c r="V65" s="35"/>
-      <c r="W65" s="35"/>
-      <c r="X65" s="35"/>
-      <c r="AU65" s="40"/>
-      <c r="AV65" s="41"/>
-      <c r="BA65" s="62"/>
-      <c r="BF65" s="35"/>
-      <c r="BT65" s="35"/>
-      <c r="BU65" s="35"/>
-      <c r="BV65" s="35"/>
-      <c r="BW65" s="36"/>
-      <c r="BX65" s="36"/>
-      <c r="BY65" s="37"/>
-      <c r="BZ65" s="36"/>
-      <c r="CA65" s="38"/>
-      <c r="CF65" s="39"/>
-      <c r="CG65" s="39"/>
-      <c r="CH65" s="39"/>
-      <c r="CI65" s="39"/>
-    </row>
-    <row r="66" spans="1:87" x14ac:dyDescent="0.3">
-      <c r="A66" s="35"/>
+      <c r="C65" s="35">
+        <v>1528</v>
+      </c>
+      <c r="D65" s="35">
+        <v>509</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="F65" s="35">
+        <v>2022</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="I65" s="35">
+        <v>1</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L65" s="1">
+        <v>448</v>
+      </c>
+      <c r="M65" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N65" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="O65" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="P65" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q65" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="R65" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="S65" s="1">
+        <v>1</v>
+      </c>
+      <c r="T65" s="1">
+        <v>1</v>
+      </c>
+      <c r="U65" s="1">
+        <v>0</v>
+      </c>
+      <c r="V65" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="W65" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="X65" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y65" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB65" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD65" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF65" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="AH65" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ65" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK65" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL65" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM65" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN65" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO65" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP65" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ65" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR65" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AS65" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="AT65" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU65" s="42">
+        <v>0.12662000000000001</v>
+      </c>
+      <c r="AV65" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="AW65" s="1">
+        <v>0.10828</v>
+      </c>
+      <c r="AX65" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="AY65" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="AZ65" s="50">
+        <f>AU65/AW65</f>
+        <v>1.1693756926486887</v>
+      </c>
+      <c r="BA65" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BB65" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BC65" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BD65" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BE65" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BF65" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BG65" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BH65" s="1">
+        <v>429</v>
+      </c>
+      <c r="BI65" s="1">
+        <v>429</v>
+      </c>
+      <c r="BJ65" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BK65" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BL65" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BM65" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BN65" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BO65" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP65" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="BQ65" s="1">
+        <v>0</v>
+      </c>
+      <c r="BR65" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="BS65" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="BT65" s="35">
+        <v>0</v>
+      </c>
+      <c r="BU65" s="35">
+        <v>0</v>
+      </c>
+      <c r="BV65" s="35">
+        <v>0</v>
+      </c>
+      <c r="BW65" s="92">
+        <f>((AZ65^2)/(AZ65^2+BH65))^(1/2)</f>
+        <v>5.6368224943018901E-2</v>
+      </c>
+      <c r="BX65" s="92">
+        <f>0.5*LN((1+BW65)/(1-BW65))</f>
+        <v>5.6428040047317683E-2</v>
+      </c>
+      <c r="BY65" s="92">
+        <f>((1-(BX65^2)^2)/(BH65-1))</f>
+        <v>2.3364249097108415E-3</v>
+      </c>
+      <c r="BZ65" s="92">
+        <f>1/(BH65-3)</f>
+        <v>2.3474178403755869E-3</v>
+      </c>
+      <c r="CA65" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="CB65" s="72">
+        <f>BH65-2</f>
+        <v>427</v>
+      </c>
+      <c r="CC65" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="CD65" s="92">
+        <f>((AZ65^2)/(AZ65^2+BI65))^(1/2)</f>
+        <v>5.6368224943018901E-2</v>
+      </c>
+      <c r="CE65" s="92">
+        <f>0.5*LN((1+CD65)/(1-CD65))</f>
+        <v>5.6428040047317683E-2</v>
+      </c>
+      <c r="CF65" s="92">
+        <f>((1-(CE65^2)^2)/(BI65-1))</f>
+        <v>2.3364249097108415E-3</v>
+      </c>
+      <c r="CG65" s="92">
+        <f>1/(BI65-3)</f>
+        <v>2.3474178403755869E-3</v>
+      </c>
+      <c r="CH65" s="72"/>
+      <c r="CI65" s="72"/>
+      <c r="CJ65" s="72"/>
+      <c r="CK65" s="1"/>
+      <c r="CL65" s="1"/>
+    </row>
+    <row r="66" spans="1:90" s="115" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="35" t="s">
+        <v>80</v>
+      </c>
       <c r="B66" s="35"/>
-      <c r="C66" s="35"/>
-      <c r="D66" s="35"/>
-      <c r="F66" s="35"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="35"/>
-      <c r="P66" s="35"/>
-      <c r="V66" s="35"/>
-      <c r="W66" s="35"/>
-      <c r="X66" s="35"/>
-      <c r="AU66" s="40"/>
-      <c r="AV66" s="41"/>
-      <c r="BA66" s="62"/>
-      <c r="BF66" s="35"/>
-      <c r="BT66" s="35"/>
-      <c r="BU66" s="35"/>
-      <c r="BV66" s="35"/>
-      <c r="BW66" s="36"/>
-      <c r="BX66" s="36"/>
-      <c r="BY66" s="37"/>
-      <c r="BZ66" s="36"/>
-      <c r="CA66" s="38"/>
-      <c r="CF66" s="39"/>
-      <c r="CG66" s="39"/>
-      <c r="CH66" s="39"/>
-      <c r="CI66" s="39"/>
-    </row>
-    <row r="67" spans="1:87" x14ac:dyDescent="0.3">
-      <c r="A67" s="35"/>
+      <c r="C66" s="35">
+        <v>1529</v>
+      </c>
+      <c r="D66" s="35">
+        <v>509</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="F66" s="35">
+        <v>2022</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="I66" s="35">
+        <v>1</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L66" s="1">
+        <v>448</v>
+      </c>
+      <c r="M66" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N66" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="O66" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="P66" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q66" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="R66" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="S66" s="1">
+        <v>1</v>
+      </c>
+      <c r="T66" s="1">
+        <v>1</v>
+      </c>
+      <c r="U66" s="1">
+        <v>0</v>
+      </c>
+      <c r="V66" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="W66" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="X66" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y66" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA66" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG66" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="AH66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK66" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ66" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR66" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AS66" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="AT66" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU66" s="42">
+        <v>1.1599999999999999E-2</v>
+      </c>
+      <c r="AV66" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="AW66" s="1">
+        <v>0.11618000000000001</v>
+      </c>
+      <c r="AX66" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="AY66" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="AZ66" s="50">
+        <f>AU66/AW66</f>
+        <v>9.9845067997934231E-2</v>
+      </c>
+      <c r="BA66" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BB66" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BC66" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BD66" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BE66" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BF66" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BG66" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BH66" s="1">
+        <v>429</v>
+      </c>
+      <c r="BI66" s="1">
+        <v>429</v>
+      </c>
+      <c r="BJ66" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BK66" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BL66" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BM66" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BN66" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BO66" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP66" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="BQ66" s="1">
+        <v>0</v>
+      </c>
+      <c r="BR66" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="BS66" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="BT66" s="35">
+        <v>0</v>
+      </c>
+      <c r="BU66" s="35">
+        <v>0</v>
+      </c>
+      <c r="BV66" s="35">
+        <v>0</v>
+      </c>
+      <c r="BW66" s="92">
+        <f>((AZ66^2)/(AZ66^2+BH66))^(1/2)</f>
+        <v>4.8205092994949329E-3</v>
+      </c>
+      <c r="BX66" s="92">
+        <f>0.5*LN((1+BW66)/(1-BW66))</f>
+        <v>4.8205466385716845E-3</v>
+      </c>
+      <c r="BY66" s="92">
+        <f>((1-(BX66^2)^2)/(BH66-1))</f>
+        <v>2.3364485968691839E-3</v>
+      </c>
+      <c r="BZ66" s="92">
+        <f>1/(BH66-3)</f>
+        <v>2.3474178403755869E-3</v>
+      </c>
+      <c r="CA66" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="CB66" s="72">
+        <f>BH66-2</f>
+        <v>427</v>
+      </c>
+      <c r="CC66" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="CD66" s="92">
+        <f>((AZ66^2)/(AZ66^2+BI66))^(1/2)</f>
+        <v>4.8205092994949329E-3</v>
+      </c>
+      <c r="CE66" s="92">
+        <f>0.5*LN((1+CD66)/(1-CD66))</f>
+        <v>4.8205466385716845E-3</v>
+      </c>
+      <c r="CF66" s="92">
+        <f>((1-(CE66^2)^2)/(BI66-1))</f>
+        <v>2.3364485968691839E-3</v>
+      </c>
+      <c r="CG66" s="92">
+        <f>1/(BI66-3)</f>
+        <v>2.3474178403755869E-3</v>
+      </c>
+      <c r="CH66" s="72"/>
+      <c r="CI66" s="72"/>
+      <c r="CJ66" s="72"/>
+      <c r="CK66" s="1"/>
+      <c r="CL66" s="1"/>
+    </row>
+    <row r="67" spans="1:90" s="115" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="35" t="s">
+        <v>80</v>
+      </c>
       <c r="B67" s="35"/>
-      <c r="C67" s="35"/>
-      <c r="D67" s="35"/>
-      <c r="F67" s="35"/>
-      <c r="I67" s="35"/>
-      <c r="P67" s="35"/>
-      <c r="V67" s="35"/>
-      <c r="W67" s="35"/>
-      <c r="X67" s="35"/>
-      <c r="AT67" s="35"/>
-      <c r="AU67" s="42"/>
-      <c r="AV67" s="41"/>
-      <c r="BA67" s="69"/>
-      <c r="BF67" s="35"/>
-      <c r="BT67" s="35"/>
-      <c r="BU67" s="35"/>
-      <c r="BV67" s="35"/>
-      <c r="BW67" s="36"/>
-      <c r="BX67" s="36"/>
-      <c r="BY67" s="37"/>
-      <c r="BZ67" s="36"/>
-      <c r="CA67" s="38"/>
-    </row>
-    <row r="68" spans="1:87" x14ac:dyDescent="0.3">
-      <c r="A68" s="35"/>
+      <c r="C67" s="35">
+        <v>1530</v>
+      </c>
+      <c r="D67" s="35">
+        <v>509</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="F67" s="35">
+        <v>2022</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="I67" s="35">
+        <v>1</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L67" s="1">
+        <v>448</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N67" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="O67" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="P67" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q67" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="R67" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="S67" s="1">
+        <v>1</v>
+      </c>
+      <c r="T67" s="1">
+        <v>1</v>
+      </c>
+      <c r="U67" s="1">
+        <v>0</v>
+      </c>
+      <c r="V67" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="W67" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="X67" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y67" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z67" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA67" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB67" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC67" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD67" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE67" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF67" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG67" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="AH67" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI67" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ67" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK67" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL67" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM67" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN67" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO67" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP67" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ67" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR67" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AS67" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="AT67" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU67" s="42">
+        <v>0.11307</v>
+      </c>
+      <c r="AV67" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="AW67" s="1">
+        <v>0.10706</v>
+      </c>
+      <c r="AX67" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="AY67" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="AZ67" s="50">
+        <f>AU67/AW67</f>
+        <v>1.0561367457500468</v>
+      </c>
+      <c r="BA67" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BB67" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BC67" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BD67" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BE67" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BF67" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BG67" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BH67" s="1">
+        <v>429</v>
+      </c>
+      <c r="BI67" s="1">
+        <v>429</v>
+      </c>
+      <c r="BJ67" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BK67" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BL67" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BM67" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BN67" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BO67" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP67" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="BQ67" s="1">
+        <v>0</v>
+      </c>
+      <c r="BR67" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="BS67" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="BT67" s="35">
+        <v>0</v>
+      </c>
+      <c r="BU67" s="35">
+        <v>0</v>
+      </c>
+      <c r="BV67" s="35">
+        <v>0</v>
+      </c>
+      <c r="BW67" s="92">
+        <f>((AZ67^2)/(AZ67^2+BH67))^(1/2)</f>
+        <v>5.092460210437183E-2</v>
+      </c>
+      <c r="BX67" s="92">
+        <f>0.5*LN((1+BW67)/(1-BW67))</f>
+        <v>5.0968691907840868E-2</v>
+      </c>
+      <c r="BY67" s="92">
+        <f>((1-(BX67^2)^2)/(BH67-1))</f>
+        <v>2.3364328303642715E-3</v>
+      </c>
+      <c r="BZ67" s="92">
+        <f>1/(BH67-3)</f>
+        <v>2.3474178403755869E-3</v>
+      </c>
+      <c r="CA67" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="CB67" s="72">
+        <f>BH67-2</f>
+        <v>427</v>
+      </c>
+      <c r="CC67" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="CD67" s="92">
+        <f>((AZ67^2)/(AZ67^2+BI67))^(1/2)</f>
+        <v>5.092460210437183E-2</v>
+      </c>
+      <c r="CE67" s="92">
+        <f>0.5*LN((1+CD67)/(1-CD67))</f>
+        <v>5.0968691907840868E-2</v>
+      </c>
+      <c r="CF67" s="92">
+        <f>((1-(CE67^2)^2)/(BI67-1))</f>
+        <v>2.3364328303642715E-3</v>
+      </c>
+      <c r="CG67" s="92">
+        <f>1/(BI67-3)</f>
+        <v>2.3474178403755869E-3</v>
+      </c>
+      <c r="CH67" s="72"/>
+      <c r="CI67" s="72"/>
+      <c r="CJ67" s="72"/>
+      <c r="CK67" s="1"/>
+      <c r="CL67" s="1"/>
+    </row>
+    <row r="68" spans="1:90" s="115" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="35" t="s">
+        <v>80</v>
+      </c>
       <c r="B68" s="35"/>
-      <c r="C68" s="35"/>
-      <c r="D68" s="35"/>
-      <c r="F68" s="35"/>
-      <c r="I68" s="35"/>
-      <c r="P68" s="35"/>
-      <c r="V68" s="35"/>
-      <c r="W68" s="35"/>
-      <c r="X68" s="35"/>
-      <c r="AT68" s="35"/>
-      <c r="AU68" s="42"/>
-      <c r="AV68" s="41"/>
-      <c r="BA68" s="69"/>
-      <c r="BF68" s="35"/>
-      <c r="BT68" s="35"/>
-      <c r="BU68" s="35"/>
-      <c r="BV68" s="35"/>
-      <c r="BW68" s="36"/>
-      <c r="BX68" s="36"/>
-      <c r="BY68" s="37"/>
-      <c r="BZ68" s="36"/>
-      <c r="CA68" s="38"/>
-    </row>
-    <row r="69" spans="1:87" x14ac:dyDescent="0.3">
-      <c r="A69" s="35"/>
+      <c r="C68" s="35">
+        <v>1531</v>
+      </c>
+      <c r="D68" s="35">
+        <v>509</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="F68" s="35">
+        <v>2022</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="I68" s="35">
+        <v>1</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L68" s="1">
+        <v>448</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N68" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="P68" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q68" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="R68" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="S68" s="1">
+        <v>1</v>
+      </c>
+      <c r="T68" s="1">
+        <v>1</v>
+      </c>
+      <c r="U68" s="1">
+        <v>0</v>
+      </c>
+      <c r="V68" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="W68" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="X68" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y68" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="AH68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK68" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ68" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR68" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AS68" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="AT68" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU68" s="42">
+        <v>0.23730000000000001</v>
+      </c>
+      <c r="AV68" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="AW68" s="1">
+        <v>0.10885</v>
+      </c>
+      <c r="AX68" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="AY68" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="AZ68" s="50">
+        <f>AU68/AW68</f>
+        <v>2.180064308681672</v>
+      </c>
+      <c r="BA68" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BB68" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BC68" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BD68" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BE68" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BF68" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BG68" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BH68" s="1">
+        <v>429</v>
+      </c>
+      <c r="BI68" s="1">
+        <v>429</v>
+      </c>
+      <c r="BJ68" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BK68" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BL68" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BM68" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BN68" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BO68" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP68" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="BQ68" s="1">
+        <v>1</v>
+      </c>
+      <c r="BR68" s="1">
+        <v>106.2</v>
+      </c>
+      <c r="BS68" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="BT68" s="35">
+        <v>0</v>
+      </c>
+      <c r="BU68" s="35">
+        <v>0</v>
+      </c>
+      <c r="BV68" s="35">
+        <v>0</v>
+      </c>
+      <c r="BW68" s="92">
+        <f>((AZ68^2)/(AZ68^2+BH68))^(1/2)</f>
+        <v>0.10467626525942129</v>
+      </c>
+      <c r="BX68" s="92">
+        <f>0.5*LN((1+BW68)/(1-BW68))</f>
+        <v>0.10506111537265546</v>
+      </c>
+      <c r="BY68" s="92">
+        <f>((1-(BX68^2)^2)/(BH68-1))</f>
+        <v>2.3361639395633057E-3</v>
+      </c>
+      <c r="BZ68" s="92">
+        <f>1/(BH68-3)</f>
+        <v>2.3474178403755869E-3</v>
+      </c>
+      <c r="CA68" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="CB68" s="72">
+        <f>BH68-2</f>
+        <v>427</v>
+      </c>
+      <c r="CC68" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="CD68" s="92">
+        <f>((AZ68^2)/(AZ68^2+BI68))^(1/2)</f>
+        <v>0.10467626525942129</v>
+      </c>
+      <c r="CE68" s="92">
+        <f>0.5*LN((1+CD68)/(1-CD68))</f>
+        <v>0.10506111537265546</v>
+      </c>
+      <c r="CF68" s="92">
+        <f>((1-(CE68^2)^2)/(BI68-1))</f>
+        <v>2.3361639395633057E-3</v>
+      </c>
+      <c r="CG68" s="92">
+        <f>1/(BI68-3)</f>
+        <v>2.3474178403755869E-3</v>
+      </c>
+      <c r="CH68" s="72"/>
+      <c r="CI68" s="72"/>
+      <c r="CJ68" s="72"/>
+      <c r="CK68" s="1"/>
+      <c r="CL68" s="1"/>
+    </row>
+    <row r="69" spans="1:90" s="115" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="35" t="s">
+        <v>80</v>
+      </c>
       <c r="B69" s="35"/>
-      <c r="C69" s="35"/>
-      <c r="D69" s="35"/>
-      <c r="F69" s="35"/>
-      <c r="I69" s="35"/>
-      <c r="P69" s="35"/>
-      <c r="V69" s="35"/>
-      <c r="W69" s="35"/>
-      <c r="X69" s="35"/>
-      <c r="AT69" s="35"/>
-      <c r="AU69" s="42"/>
-      <c r="AV69" s="41"/>
-      <c r="BA69" s="69"/>
-      <c r="BT69" s="35"/>
-      <c r="BU69" s="35"/>
-      <c r="BV69" s="35"/>
-      <c r="BW69" s="36"/>
-      <c r="BX69" s="36"/>
-      <c r="BY69" s="37"/>
-      <c r="BZ69" s="36"/>
-      <c r="CA69" s="38"/>
-    </row>
-    <row r="70" spans="1:87" x14ac:dyDescent="0.3">
-      <c r="A70" s="35"/>
+      <c r="C69" s="35">
+        <v>1532</v>
+      </c>
+      <c r="D69" s="35">
+        <v>509</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="F69" s="35">
+        <v>2022</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="I69" s="35">
+        <v>1</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L69" s="1">
+        <v>448</v>
+      </c>
+      <c r="M69" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N69" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="O69" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="P69" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q69" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="R69" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="S69" s="1">
+        <v>1</v>
+      </c>
+      <c r="T69" s="1">
+        <v>1</v>
+      </c>
+      <c r="U69" s="1">
+        <v>0</v>
+      </c>
+      <c r="V69" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="W69" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="X69" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y69" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB69" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD69" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF69" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="AH69" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ69" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL69" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM69" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN69" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO69" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP69" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ69" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR69" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AS69" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="AT69" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU69" s="42">
+        <v>0.20735999999999999</v>
+      </c>
+      <c r="AV69" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="AW69" s="1">
+        <v>0.11491</v>
+      </c>
+      <c r="AX69" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="AY69" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="AZ69" s="50">
+        <f>AU69/AW69</f>
+        <v>1.8045426855800191</v>
+      </c>
+      <c r="BA69" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BB69" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BC69" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BD69" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BE69" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BF69" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BG69" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BH69" s="1">
+        <v>429</v>
+      </c>
+      <c r="BI69" s="1">
+        <v>429</v>
+      </c>
+      <c r="BJ69" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BK69" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BL69" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BM69" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BN69" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BO69" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP69" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="BQ69" s="1">
+        <v>1</v>
+      </c>
+      <c r="BR69" s="1">
+        <v>84.92</v>
+      </c>
+      <c r="BS69" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="BT69" s="35">
+        <v>0</v>
+      </c>
+      <c r="BU69" s="35">
+        <v>0</v>
+      </c>
+      <c r="BV69" s="35">
+        <v>0</v>
+      </c>
+      <c r="BW69" s="92">
+        <f>((AZ69^2)/(AZ69^2+BH69))^(1/2)</f>
+        <v>8.6795349517998721E-2</v>
+      </c>
+      <c r="BX69" s="92">
+        <f>0.5*LN((1+BW69)/(1-BW69))</f>
+        <v>8.7014295664345515E-2</v>
+      </c>
+      <c r="BY69" s="92">
+        <f>((1-(BX69^2)^2)/(BH69-1))</f>
+        <v>2.3363146555485199E-3</v>
+      </c>
+      <c r="BZ69" s="92">
+        <f>1/(BH69-3)</f>
+        <v>2.3474178403755869E-3</v>
+      </c>
+      <c r="CA69" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="CB69" s="72">
+        <f>BH69-2</f>
+        <v>427</v>
+      </c>
+      <c r="CC69" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="CD69" s="92">
+        <f>((AZ69^2)/(AZ69^2+BI69))^(1/2)</f>
+        <v>8.6795349517998721E-2</v>
+      </c>
+      <c r="CE69" s="92">
+        <f>0.5*LN((1+CD69)/(1-CD69))</f>
+        <v>8.7014295664345515E-2</v>
+      </c>
+      <c r="CF69" s="92">
+        <f>((1-(CE69^2)^2)/(BI69-1))</f>
+        <v>2.3363146555485199E-3</v>
+      </c>
+      <c r="CG69" s="92">
+        <f>1/(BI69-3)</f>
+        <v>2.3474178403755869E-3</v>
+      </c>
+      <c r="CH69" s="72"/>
+      <c r="CI69" s="72"/>
+      <c r="CJ69" s="72"/>
+      <c r="CK69" s="1"/>
+      <c r="CL69" s="1"/>
+    </row>
+    <row r="70" spans="1:90" s="115" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="35" t="s">
+        <v>80</v>
+      </c>
       <c r="B70" s="35"/>
-      <c r="C70" s="35"/>
-      <c r="D70" s="35"/>
-      <c r="F70" s="35"/>
-      <c r="I70" s="35"/>
-      <c r="P70" s="35"/>
-      <c r="V70" s="35"/>
-      <c r="W70" s="35"/>
-      <c r="X70" s="35"/>
-      <c r="AT70" s="35"/>
-      <c r="AU70" s="42"/>
-      <c r="AV70" s="41"/>
-      <c r="BA70" s="69"/>
-      <c r="BT70" s="35"/>
-      <c r="BU70" s="35"/>
-      <c r="BV70" s="35"/>
-      <c r="BW70" s="36"/>
-      <c r="BX70" s="36"/>
-      <c r="BY70" s="37"/>
-      <c r="BZ70" s="36"/>
-      <c r="CA70" s="38"/>
-    </row>
-    <row r="71" spans="1:87" x14ac:dyDescent="0.3">
-      <c r="A71" s="35"/>
+      <c r="C70" s="35">
+        <v>1533</v>
+      </c>
+      <c r="D70" s="35">
+        <v>509</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="F70" s="35">
+        <v>2022</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="I70" s="35">
+        <v>1</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L70" s="1">
+        <v>448</v>
+      </c>
+      <c r="M70" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N70" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="O70" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="P70" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q70" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="R70" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="S70" s="1">
+        <v>1</v>
+      </c>
+      <c r="T70" s="1">
+        <v>1</v>
+      </c>
+      <c r="U70" s="1">
+        <v>0</v>
+      </c>
+      <c r="V70" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="W70" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="X70" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y70" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB70" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF70" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="AH70" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ70" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL70" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM70" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN70" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO70" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP70" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ70" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR70" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AS70" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="AT70" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU70" s="42">
+        <v>0.18368000000000001</v>
+      </c>
+      <c r="AV70" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="AW70" s="1">
+        <v>0.12373000000000001</v>
+      </c>
+      <c r="AX70" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="AY70" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="AZ70" s="50">
+        <f>AU70/AW70</f>
+        <v>1.4845227511517012</v>
+      </c>
+      <c r="BA70" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BB70" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BC70" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BD70" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BE70" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BF70" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BG70" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BH70" s="1">
+        <v>429</v>
+      </c>
+      <c r="BI70" s="1">
+        <v>429</v>
+      </c>
+      <c r="BJ70" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BK70" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BL70" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BM70" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BN70" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BO70" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP70" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="BQ70" s="1">
+        <v>1</v>
+      </c>
+      <c r="BR70" s="1">
+        <v>67.98</v>
+      </c>
+      <c r="BS70" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="BT70" s="35">
+        <v>0</v>
+      </c>
+      <c r="BU70" s="35">
+        <v>0</v>
+      </c>
+      <c r="BV70" s="35">
+        <v>0</v>
+      </c>
+      <c r="BW70" s="92">
+        <f>((AZ70^2)/(AZ70^2+BH70))^(1/2)</f>
+        <v>7.1490043964920355E-2</v>
+      </c>
+      <c r="BX70" s="92">
+        <f>0.5*LN((1+BW70)/(1-BW70))</f>
+        <v>7.1612209873236576E-2</v>
+      </c>
+      <c r="BY70" s="92">
+        <f>((1-(BX70^2)^2)/(BH70-1))</f>
+        <v>2.3363871505861522E-3</v>
+      </c>
+      <c r="BZ70" s="92">
+        <f>1/(BH70-3)</f>
+        <v>2.3474178403755869E-3</v>
+      </c>
+      <c r="CA70" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="CB70" s="72">
+        <f>BH70-2</f>
+        <v>427</v>
+      </c>
+      <c r="CC70" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="CD70" s="92">
+        <f>((AZ70^2)/(AZ70^2+BI70))^(1/2)</f>
+        <v>7.1490043964920355E-2</v>
+      </c>
+      <c r="CE70" s="92">
+        <f>0.5*LN((1+CD70)/(1-CD70))</f>
+        <v>7.1612209873236576E-2</v>
+      </c>
+      <c r="CF70" s="92">
+        <f>((1-(CE70^2)^2)/(BI70-1))</f>
+        <v>2.3363871505861522E-3</v>
+      </c>
+      <c r="CG70" s="92">
+        <f>1/(BI70-3)</f>
+        <v>2.3474178403755869E-3</v>
+      </c>
+      <c r="CH70" s="72"/>
+      <c r="CI70" s="72"/>
+      <c r="CJ70" s="72"/>
+      <c r="CK70" s="1"/>
+      <c r="CL70" s="1"/>
+    </row>
+    <row r="71" spans="1:90" s="115" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="35" t="s">
+        <v>80</v>
+      </c>
       <c r="B71" s="35"/>
-      <c r="C71" s="35"/>
-      <c r="D71" s="35"/>
-      <c r="F71" s="35"/>
-      <c r="I71" s="35"/>
-      <c r="P71" s="35"/>
-      <c r="V71" s="35"/>
-      <c r="W71" s="35"/>
-      <c r="X71" s="35"/>
-      <c r="AT71" s="35"/>
-      <c r="AU71" s="42"/>
-      <c r="AV71" s="41"/>
-      <c r="BA71" s="69"/>
-      <c r="BT71" s="35"/>
-      <c r="BU71" s="35"/>
-      <c r="BV71" s="35"/>
-      <c r="BW71" s="36"/>
-      <c r="BX71" s="36"/>
-      <c r="BY71" s="37"/>
-      <c r="BZ71" s="36"/>
-      <c r="CA71" s="38"/>
-    </row>
-    <row r="72" spans="1:87" x14ac:dyDescent="0.3">
-      <c r="A72" s="35"/>
+      <c r="C71" s="35">
+        <v>1534</v>
+      </c>
+      <c r="D71" s="35">
+        <v>509</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="F71" s="35">
+        <v>2022</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="I71" s="35">
+        <v>1</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L71" s="1">
+        <v>448</v>
+      </c>
+      <c r="M71" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N71" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="O71" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="P71" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q71" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="R71" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="S71" s="1">
+        <v>1</v>
+      </c>
+      <c r="T71" s="1">
+        <v>1</v>
+      </c>
+      <c r="U71" s="1">
+        <v>0</v>
+      </c>
+      <c r="V71" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="W71" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="X71" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y71" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB71" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD71" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF71" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="AH71" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ71" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL71" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM71" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN71" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP71" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ71" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR71" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AS71" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="AT71" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU71" s="42">
+        <v>0.70982000000000001</v>
+      </c>
+      <c r="AV71" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="AW71" s="1">
+        <v>0.13383999999999999</v>
+      </c>
+      <c r="AX71" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="AY71" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="AZ71" s="50">
+        <f>AU71/AW71</f>
+        <v>5.303496712492529</v>
+      </c>
+      <c r="BA71" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BB71" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BC71" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BD71" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BE71" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BF71" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BG71" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BH71" s="1">
+        <v>429</v>
+      </c>
+      <c r="BI71" s="1">
+        <v>429</v>
+      </c>
+      <c r="BJ71" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BK71" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BL71" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BM71" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BN71" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BO71" s="1">
+        <v>1</v>
+      </c>
+      <c r="BP71" s="1">
+        <v>26.5</v>
+      </c>
+      <c r="BQ71" s="1">
+        <v>0</v>
+      </c>
+      <c r="BR71" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="BS71" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="BT71" s="35">
+        <v>0</v>
+      </c>
+      <c r="BU71" s="35">
+        <v>0</v>
+      </c>
+      <c r="BV71" s="35">
+        <v>0</v>
+      </c>
+      <c r="BW71" s="92">
+        <f>((AZ71^2)/(AZ71^2+BH71))^(1/2)</f>
+        <v>0.24805262683143273</v>
+      </c>
+      <c r="BX71" s="92">
+        <f>0.5*LN((1+BW71)/(1-BW71))</f>
+        <v>0.25333668898169365</v>
+      </c>
+      <c r="BY71" s="92">
+        <f>((1-(BX71^2)^2)/(BH71-1))</f>
+        <v>2.3268247537515763E-3</v>
+      </c>
+      <c r="BZ71" s="92">
+        <f>1/(BH71-3)</f>
+        <v>2.3474178403755869E-3</v>
+      </c>
+      <c r="CA71" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="CB71" s="72">
+        <f>BH71-2</f>
+        <v>427</v>
+      </c>
+      <c r="CC71" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="CD71" s="92">
+        <f>((AZ71^2)/(AZ71^2+BI71))^(1/2)</f>
+        <v>0.24805262683143273</v>
+      </c>
+      <c r="CE71" s="92">
+        <f>0.5*LN((1+CD71)/(1-CD71))</f>
+        <v>0.25333668898169365</v>
+      </c>
+      <c r="CF71" s="92">
+        <f>((1-(CE71^2)^2)/(BI71-1))</f>
+        <v>2.3268247537515763E-3</v>
+      </c>
+      <c r="CG71" s="92">
+        <f>1/(BI71-3)</f>
+        <v>2.3474178403755869E-3</v>
+      </c>
+      <c r="CH71" s="72"/>
+      <c r="CI71" s="72"/>
+      <c r="CJ71" s="72"/>
+      <c r="CK71" s="1"/>
+      <c r="CL71" s="1"/>
+    </row>
+    <row r="72" spans="1:90" s="115" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="35" t="s">
+        <v>80</v>
+      </c>
       <c r="B72" s="35"/>
-      <c r="C72" s="35"/>
-      <c r="D72" s="35"/>
-      <c r="F72" s="35"/>
-      <c r="I72" s="35"/>
-      <c r="P72" s="35"/>
-      <c r="V72" s="35"/>
-      <c r="W72" s="35"/>
-      <c r="X72" s="35"/>
-      <c r="AT72" s="35"/>
-      <c r="AU72" s="42"/>
-      <c r="AV72" s="41"/>
-      <c r="BA72" s="69"/>
-      <c r="BT72" s="35"/>
-      <c r="BU72" s="35"/>
-      <c r="BV72" s="35"/>
-      <c r="BW72" s="36"/>
-      <c r="BX72" s="36"/>
-      <c r="BY72" s="37"/>
-      <c r="BZ72" s="36"/>
-      <c r="CA72" s="38"/>
-    </row>
-    <row r="73" spans="1:87" x14ac:dyDescent="0.3">
-      <c r="A73" s="35"/>
+      <c r="C72" s="35">
+        <v>1535</v>
+      </c>
+      <c r="D72" s="35">
+        <v>509</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="F72" s="35">
+        <v>2022</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="I72" s="35">
+        <v>1</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L72" s="1">
+        <v>448</v>
+      </c>
+      <c r="M72" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N72" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="O72" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="P72" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q72" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="R72" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="S72" s="1">
+        <v>1</v>
+      </c>
+      <c r="T72" s="1">
+        <v>1</v>
+      </c>
+      <c r="U72" s="1">
+        <v>0</v>
+      </c>
+      <c r="V72" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="W72" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="X72" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y72" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z72" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA72" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB72" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC72" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD72" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE72" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF72" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG72" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="AH72" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI72" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ72" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK72" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL72" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM72" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN72" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO72" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP72" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ72" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR72" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AS72" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="AT72" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU72" s="42">
+        <v>0.87841000000000002</v>
+      </c>
+      <c r="AV72" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="AW72" s="1">
+        <v>0.14804</v>
+      </c>
+      <c r="AX72" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="AY72" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="AZ72" s="50">
+        <f>AU72/AW72</f>
+        <v>5.9335990272899215</v>
+      </c>
+      <c r="BA72" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BB72" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BC72" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BD72" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BE72" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BF72" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BG72" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BH72" s="1">
+        <v>429</v>
+      </c>
+      <c r="BI72" s="1">
+        <v>429</v>
+      </c>
+      <c r="BJ72" s="94" t="s">
+        <v>83</v>
+      </c>
+      <c r="BK72" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BL72" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BM72" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BN72" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BO72" s="1">
+        <v>1</v>
+      </c>
+      <c r="BP72" s="1">
+        <v>47.78</v>
+      </c>
+      <c r="BQ72" s="1">
+        <v>0</v>
+      </c>
+      <c r="BR72" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="BS72" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="BT72" s="35">
+        <v>0</v>
+      </c>
+      <c r="BU72" s="35">
+        <v>0</v>
+      </c>
+      <c r="BV72" s="35">
+        <v>0</v>
+      </c>
+      <c r="BW72" s="92">
+        <f>((AZ72^2)/(AZ72^2+BH72))^(1/2)</f>
+        <v>0.27539881853597031</v>
+      </c>
+      <c r="BX72" s="92">
+        <f>0.5*LN((1+BW72)/(1-BW72))</f>
+        <v>0.28269639928405588</v>
+      </c>
+      <c r="BY72" s="92">
+        <f>((1-(BX72^2)^2)/(BH72-1))</f>
+        <v>2.3215262441266824E-3</v>
+      </c>
+      <c r="BZ72" s="92">
+        <f>1/(BH72-3)</f>
+        <v>2.3474178403755869E-3</v>
+      </c>
+      <c r="CA72" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="CB72" s="72">
+        <f>BH72-2</f>
+        <v>427</v>
+      </c>
+      <c r="CC72" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="CD72" s="92">
+        <f>((AZ72^2)/(AZ72^2+BI72))^(1/2)</f>
+        <v>0.27539881853597031</v>
+      </c>
+      <c r="CE72" s="92">
+        <f>0.5*LN((1+CD72)/(1-CD72))</f>
+        <v>0.28269639928405588</v>
+      </c>
+      <c r="CF72" s="92">
+        <f>((1-(CE72^2)^2)/(BI72-1))</f>
+        <v>2.3215262441266824E-3</v>
+      </c>
+      <c r="CG72" s="92">
+        <f>1/(BI72-3)</f>
+        <v>2.3474178403755869E-3</v>
+      </c>
+      <c r="CH72" s="72"/>
+      <c r="CI72" s="72"/>
+      <c r="CJ72" s="72"/>
+      <c r="CK72" s="1"/>
+      <c r="CL72" s="1"/>
+    </row>
+    <row r="73" spans="1:90" s="115" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="35" t="s">
+        <v>80</v>
+      </c>
       <c r="B73" s="35"/>
-      <c r="C73" s="35"/>
-      <c r="D73" s="35"/>
-      <c r="F73" s="35"/>
-      <c r="I73" s="35"/>
-      <c r="P73" s="35"/>
-      <c r="V73" s="35"/>
-      <c r="W73" s="35"/>
-      <c r="AU73" s="42"/>
-      <c r="AV73" s="41"/>
-      <c r="BW73" s="36"/>
-      <c r="BX73" s="36"/>
-      <c r="BY73" s="37"/>
-      <c r="BZ73" s="36"/>
-      <c r="CA73" s="38"/>
-    </row>
-    <row r="74" spans="1:87" x14ac:dyDescent="0.3">
+      <c r="C73" s="35">
+        <v>1536</v>
+      </c>
+      <c r="D73" s="35">
+        <v>509</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="F73" s="35">
+        <v>2022</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="I73" s="35">
+        <v>1</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L73" s="1">
+        <v>448</v>
+      </c>
+      <c r="M73" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N73" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="O73" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="P73" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q73" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="R73" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="S73" s="1">
+        <v>1</v>
+      </c>
+      <c r="T73" s="1">
+        <v>1</v>
+      </c>
+      <c r="U73" s="1">
+        <v>0</v>
+      </c>
+      <c r="V73" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="W73" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="X73" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y73" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="AH73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR73" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AS73" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="AT73" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU73" s="42">
+        <v>0.37043999999999999</v>
+      </c>
+      <c r="AV73" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="AW73" s="1">
+        <v>0.10559</v>
+      </c>
+      <c r="AX73" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="AY73" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="AZ73" s="50">
+        <f>AU73/AW73</f>
+        <v>3.5082867695804527</v>
+      </c>
+      <c r="BA73" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BB73" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BC73" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BD73" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BE73" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BF73" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BG73" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="BH73" s="1">
+        <v>429</v>
+      </c>
+      <c r="BI73" s="1">
+        <v>429</v>
+      </c>
+      <c r="BJ73" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BK73" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BL73" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BM73" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BN73" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="BO73" s="1">
+        <v>1</v>
+      </c>
+      <c r="BP73" s="1">
+        <v>64.72</v>
+      </c>
+      <c r="BQ73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BR73" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="BS73" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="BT73" s="35">
+        <v>0</v>
+      </c>
+      <c r="BU73" s="35">
+        <v>0</v>
+      </c>
+      <c r="BV73" s="35">
+        <v>0</v>
+      </c>
+      <c r="BW73" s="92">
+        <f>((AZ73^2)/(AZ73^2+BH73))^(1/2)</f>
+        <v>0.16700295203362051</v>
+      </c>
+      <c r="BX73" s="92">
+        <f>0.5*LN((1+BW73)/(1-BW73))</f>
+        <v>0.16858203178623618</v>
+      </c>
+      <c r="BY73" s="92">
+        <f>((1-(BX73^2)^2)/(BH73-1))</f>
+        <v>2.3345614700983034E-3</v>
+      </c>
+      <c r="BZ73" s="92">
+        <f>1/(BH73-3)</f>
+        <v>2.3474178403755869E-3</v>
+      </c>
+      <c r="CA73" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="CB73" s="72">
+        <f>BH73-2</f>
+        <v>427</v>
+      </c>
+      <c r="CC73" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="CD73" s="92">
+        <f>((AZ73^2)/(AZ73^2+BI73))^(1/2)</f>
+        <v>0.16700295203362051</v>
+      </c>
+      <c r="CE73" s="92">
+        <f>0.5*LN((1+CD73)/(1-CD73))</f>
+        <v>0.16858203178623618</v>
+      </c>
+      <c r="CF73" s="92">
+        <f>((1-(CE73^2)^2)/(BI73-1))</f>
+        <v>2.3345614700983034E-3</v>
+      </c>
+      <c r="CG73" s="92">
+        <f>1/(BI73-3)</f>
+        <v>2.3474178403755869E-3</v>
+      </c>
+      <c r="CH73" s="72"/>
+      <c r="CI73" s="72"/>
+      <c r="CJ73" s="72"/>
+      <c r="CK73" s="1"/>
+      <c r="CL73" s="1"/>
+    </row>
+    <row r="74" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A74" s="35"/>
       <c r="B74" s="35"/>
       <c r="C74" s="35"/>
@@ -17229,7 +20715,7 @@
       <c r="BZ74" s="36"/>
       <c r="CA74" s="38"/>
     </row>
-    <row r="75" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A75" s="35"/>
       <c r="B75" s="35"/>
       <c r="C75" s="35"/>
@@ -17253,7 +20739,7 @@
       <c r="BZ75" s="36"/>
       <c r="CA75" s="38"/>
     </row>
-    <row r="76" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A76" s="35"/>
       <c r="B76" s="35"/>
       <c r="C76" s="35"/>
@@ -17277,7 +20763,7 @@
       <c r="BZ76" s="36"/>
       <c r="CA76" s="38"/>
     </row>
-    <row r="77" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A77" s="35"/>
       <c r="B77" s="35"/>
       <c r="C77" s="35"/>
@@ -17302,7 +20788,7 @@
       <c r="BZ77" s="36"/>
       <c r="CA77" s="38"/>
     </row>
-    <row r="78" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A78" s="35"/>
       <c r="B78" s="35"/>
       <c r="C78" s="35"/>
@@ -17326,7 +20812,7 @@
       <c r="BZ78" s="36"/>
       <c r="CA78" s="38"/>
     </row>
-    <row r="79" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A79" s="35"/>
       <c r="B79" s="35"/>
       <c r="C79" s="35"/>
@@ -17350,7 +20836,7 @@
       <c r="BZ79" s="36"/>
       <c r="CA79" s="38"/>
     </row>
-    <row r="80" spans="1:87" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:90" x14ac:dyDescent="0.3">
       <c r="A80" s="35"/>
       <c r="B80" s="35"/>
       <c r="C80" s="35"/>
@@ -24712,20 +28198,20 @@
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S21:S53 U21:U53 AH21:AP53">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S21:S53 U21:U53 AH21:AP53 AH60:AP64 U60:U64 S60:S64">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="I21:I53">
+    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please fill in either 1 or 0_x000a_If the Study is:_x000a_Usage - 1_x000a_Purchase - 0" promptTitle="If Study = Usage/Purchase" prompt="If the Study is:_x000a_Usage - 1_x000a_Purchase - 2" sqref="I21:I53 I60:I64">
       <formula1>0</formula1>
       <formula2>2</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="AD21:AG53"/>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="Y21:AC53">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="AD21:AG53 AD60:AG64"/>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="int" error="Choose 1 or 0" promptTitle="Intervention" prompt="Yes - 1_x000a_No - 0" sqref="Y21:AC53 Y60:AC64">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BM21:BM31 BM34:BM53"/>
+    <dataValidation errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BM21:BM31 BM34:BM53 BM60:BM64"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -24737,25 +28223,25 @@
           <x14:formula1>
             <xm:f>'Lists for variables'!$F$2:$F$30</xm:f>
           </x14:formula1>
-          <xm:sqref>M1:M20 M54:M1048576</xm:sqref>
+          <xm:sqref>M1:M20 M54:M59 M74:M1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$D$2:$D$6</xm:f>
           </x14:formula1>
-          <xm:sqref>N1:N20 N54:N1048576</xm:sqref>
+          <xm:sqref>N1:N20 N54:N59 N74:N1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$H$2:$H$7</xm:f>
           </x14:formula1>
-          <xm:sqref>Q1:Q20 Q54:Q1048576</xm:sqref>
+          <xm:sqref>Q1:Q20 Q54:Q59 Q74:Q1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Lists for variables'!$L$2:$L$10</xm:f>
           </x14:formula1>
-          <xm:sqref>R1:R20 R54:R1048576</xm:sqref>
+          <xm:sqref>R1:R20 R54:R59 R74:R1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -24792,13 +28278,13 @@
   <sheetData>
     <row r="1" spans="1:19" s="67" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="67" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B1" s="67" t="s">
         <v>17</v>
       </c>
       <c r="C1" s="68" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D1" s="67" t="s">
         <v>11</v>
@@ -24810,7 +28296,7 @@
         <v>10</v>
       </c>
       <c r="G1" s="67" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H1" s="68" t="s">
         <v>14</v>
@@ -24822,7 +28308,7 @@
         <v>8</v>
       </c>
       <c r="K1" s="67" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L1" s="67" t="s">
         <v>15</v>
@@ -24857,7 +28343,7 @@
         <v>119</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
@@ -24875,13 +28361,13 @@
         <v>97</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>95</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>87</v>
@@ -24893,13 +28379,13 @@
         <v>111</v>
       </c>
       <c r="P2" s="43" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R2" s="59" t="s">
+        <v>232</v>
+      </c>
+      <c r="S2" s="59" t="s">
         <v>233</v>
-      </c>
-      <c r="S2" s="59" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="26" x14ac:dyDescent="0.3">
@@ -24907,10 +28393,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>102</v>
@@ -24922,7 +28408,7 @@
         <v>143</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>135</v>
@@ -24931,19 +28417,19 @@
         <v>91</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>90</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>82</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>147</v>
@@ -24952,10 +28438,10 @@
         <v>96</v>
       </c>
       <c r="R3" s="50" t="s">
+        <v>238</v>
+      </c>
+      <c r="S3" s="50" t="s">
         <v>239</v>
-      </c>
-      <c r="S3" s="50" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="39" x14ac:dyDescent="0.3">
@@ -24975,16 +28461,16 @@
         <v>3</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>105</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>145</v>
@@ -24993,19 +28479,19 @@
         <v>108</v>
       </c>
       <c r="N4" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="P4" s="43" t="s">
         <v>243</v>
       </c>
-      <c r="O4" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="P4" s="43" t="s">
+      <c r="R4" s="61" t="s">
         <v>244</v>
       </c>
-      <c r="R4" s="61" t="s">
+      <c r="S4" s="61" t="s">
         <v>245</v>
-      </c>
-      <c r="S4" s="61" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="39" x14ac:dyDescent="0.3">
@@ -25019,48 +28505,48 @@
         <v>114</v>
       </c>
       <c r="H5" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="J5" s="43" t="s">
         <v>247</v>
       </c>
-      <c r="J5" s="43" t="s">
+      <c r="L5" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="M5" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="M5" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="N5" s="1" t="s">
+      <c r="O5" s="43" t="s">
         <v>250</v>
       </c>
-      <c r="O5" s="43" t="s">
+      <c r="P5" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="R5" s="50" t="s">
         <v>251</v>
       </c>
-      <c r="P5" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="R5" s="50" t="s">
+      <c r="S5" s="50" t="s">
         <v>252</v>
-      </c>
-      <c r="S5" s="50" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="D6" s="43" t="s">
+        <v>253</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>254</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>255</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>104</v>
       </c>
       <c r="J6" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="L6" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>257</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>94</v>
@@ -25069,10 +28555,10 @@
         <v>83</v>
       </c>
       <c r="R6" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="S6" s="50" t="s">
         <v>258</v>
-      </c>
-      <c r="S6" s="50" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
@@ -25083,7 +28569,7 @@
         <v>88</v>
       </c>
       <c r="J7" s="43" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L7" s="1" t="s">
         <v>89</v>
@@ -25092,163 +28578,163 @@
         <v>138</v>
       </c>
       <c r="O7" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="R7" s="50" t="s">
         <v>261</v>
       </c>
-      <c r="R7" s="50" t="s">
+      <c r="S7" s="50" t="s">
         <v>262</v>
-      </c>
-      <c r="S7" s="50" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="F8" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="J8" s="43" t="s">
         <v>264</v>
       </c>
-      <c r="J8" s="43" t="s">
+      <c r="L8" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="N8" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="L8" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="N8" s="1" t="s">
+      <c r="R8" s="50" t="s">
         <v>266</v>
       </c>
-      <c r="R8" s="50" t="s">
+      <c r="S8" s="50" t="s">
         <v>267</v>
-      </c>
-      <c r="S8" s="50" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="F9" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="L9" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="L9" s="1" t="s">
+      <c r="N9" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="N9" s="1" t="s">
+      <c r="R9" s="61" t="s">
         <v>271</v>
       </c>
-      <c r="R9" s="61" t="s">
+      <c r="S9" s="61" t="s">
         <v>272</v>
-      </c>
-      <c r="S9" s="61" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="F10" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>275</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>109</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="R10" s="61" t="s">
+        <v>275</v>
+      </c>
+      <c r="S10" s="61" t="s">
         <v>276</v>
-      </c>
-      <c r="S10" s="61" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="F11" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="J11" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="N11" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="N11" s="1" t="s">
+      <c r="R11" s="61" t="s">
         <v>280</v>
       </c>
-      <c r="R11" s="61" t="s">
+      <c r="S11" s="61" t="s">
         <v>281</v>
-      </c>
-      <c r="S11" s="61" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="F12" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="N12" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="N12" s="1" t="s">
+      <c r="R12" s="61" t="s">
         <v>284</v>
       </c>
-      <c r="R12" s="61" t="s">
+      <c r="S12" s="61" t="s">
         <v>285</v>
-      </c>
-      <c r="S12" s="61" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="F13" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="N13" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="N13" s="1" t="s">
+      <c r="R13" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="R13" s="50" t="s">
+      <c r="S13" s="50" t="s">
         <v>289</v>
-      </c>
-      <c r="S13" s="50" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="F14" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N14" s="1" t="s">
         <v>103</v>
       </c>
       <c r="R14" s="61" t="s">
+        <v>291</v>
+      </c>
+      <c r="S14" s="61" t="s">
         <v>292</v>
-      </c>
-      <c r="S14" s="61" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="F15" s="43" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="N15" s="1" t="s">
         <v>118</v>
       </c>
       <c r="R15" s="50" t="s">
+        <v>293</v>
+      </c>
+      <c r="S15" s="50" t="s">
         <v>294</v>
-      </c>
-      <c r="S15" s="50" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="F16" s="43" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="N16" s="1" t="s">
         <v>113</v>
       </c>
       <c r="R16" s="50" t="s">
+        <v>296</v>
+      </c>
+      <c r="S16" s="50" t="s">
         <v>297</v>
-      </c>
-      <c r="S16" s="50" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="17" spans="6:19" x14ac:dyDescent="0.3">
@@ -25259,38 +28745,38 @@
         <v>134</v>
       </c>
       <c r="R17" s="61" t="s">
+        <v>298</v>
+      </c>
+      <c r="S17" s="61" t="s">
         <v>299</v>
-      </c>
-      <c r="S17" s="61" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="18" spans="6:19" x14ac:dyDescent="0.3">
       <c r="F18" s="43" t="s">
+        <v>300</v>
+      </c>
+      <c r="N18" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="N18" s="1" t="s">
+      <c r="R18" s="50" t="s">
         <v>302</v>
       </c>
-      <c r="R18" s="50" t="s">
+      <c r="S18" s="50" t="s">
         <v>303</v>
-      </c>
-      <c r="S18" s="50" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="19" spans="6:19" x14ac:dyDescent="0.3">
       <c r="F19" s="43" t="s">
+        <v>304</v>
+      </c>
+      <c r="N19" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="N19" s="1" t="s">
+      <c r="R19" s="61" t="s">
         <v>306</v>
       </c>
-      <c r="R19" s="61" t="s">
+      <c r="S19" s="1" t="s">
         <v>307</v>
-      </c>
-      <c r="S19" s="1" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="20" spans="6:19" x14ac:dyDescent="0.3">
@@ -25298,41 +28784,41 @@
         <v>112</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="R20" s="50" t="s">
+        <v>308</v>
+      </c>
+      <c r="S20" s="50" t="s">
         <v>309</v>
-      </c>
-      <c r="S20" s="50" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="21" spans="6:19" x14ac:dyDescent="0.3">
       <c r="F21" s="43" t="s">
+        <v>310</v>
+      </c>
+      <c r="N21" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="N21" s="1" t="s">
+      <c r="R21" s="61" t="s">
         <v>312</v>
       </c>
-      <c r="R21" s="61" t="s">
+      <c r="S21" s="61" t="s">
         <v>313</v>
-      </c>
-      <c r="S21" s="61" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="22" spans="6:19" x14ac:dyDescent="0.3">
       <c r="F22" s="43" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N22" s="1" t="s">
         <v>139</v>
       </c>
       <c r="R22" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="S22" s="50" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="23" spans="6:19" x14ac:dyDescent="0.3">
@@ -25340,133 +28826,133 @@
         <v>81</v>
       </c>
       <c r="N23" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="R23" s="61" t="s">
         <v>316</v>
       </c>
-      <c r="R23" s="61" t="s">
+      <c r="S23" s="61" t="s">
         <v>317</v>
-      </c>
-      <c r="S23" s="61" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="24" spans="6:19" x14ac:dyDescent="0.3">
       <c r="F24" s="43" t="s">
+        <v>318</v>
+      </c>
+      <c r="N24" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="N24" s="1" t="s">
+      <c r="R24" s="61" t="s">
         <v>320</v>
       </c>
-      <c r="R24" s="61" t="s">
+      <c r="S24" s="61" t="s">
         <v>321</v>
-      </c>
-      <c r="S24" s="61" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="25" spans="6:19" x14ac:dyDescent="0.3">
       <c r="F25" s="43" t="s">
+        <v>322</v>
+      </c>
+      <c r="N25" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="N25" s="1" t="s">
+      <c r="R25" s="61" t="s">
         <v>324</v>
       </c>
-      <c r="R25" s="61" t="s">
+      <c r="S25" s="61" t="s">
         <v>325</v>
-      </c>
-      <c r="S25" s="61" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="26" spans="6:19" x14ac:dyDescent="0.3">
       <c r="F26" s="43" t="s">
+        <v>326</v>
+      </c>
+      <c r="N26" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="N26" s="1" t="s">
+      <c r="R26" s="61" t="s">
         <v>328</v>
       </c>
-      <c r="R26" s="61" t="s">
+      <c r="S26" s="61" t="s">
         <v>329</v>
-      </c>
-      <c r="S26" s="61" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="27" spans="6:19" x14ac:dyDescent="0.3">
       <c r="F27" s="43" t="s">
+        <v>330</v>
+      </c>
+      <c r="N27" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="N27" s="1" t="s">
+      <c r="R27" s="61" t="s">
         <v>332</v>
       </c>
-      <c r="R27" s="61" t="s">
+      <c r="S27" s="61" t="s">
         <v>333</v>
-      </c>
-      <c r="S27" s="61" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="28" spans="6:19" x14ac:dyDescent="0.3">
       <c r="F28" s="43" t="s">
+        <v>334</v>
+      </c>
+      <c r="N28" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="N28" s="1" t="s">
+      <c r="R28" s="61" t="s">
         <v>336</v>
       </c>
-      <c r="R28" s="61" t="s">
+      <c r="S28" s="61" t="s">
         <v>337</v>
-      </c>
-      <c r="S28" s="61" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="29" spans="6:19" x14ac:dyDescent="0.3">
       <c r="F29" s="43" t="s">
+        <v>338</v>
+      </c>
+      <c r="N29" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="N29" s="1" t="s">
+      <c r="R29" s="61" t="s">
         <v>340</v>
       </c>
-      <c r="R29" s="61" t="s">
+      <c r="S29" s="61" t="s">
         <v>341</v>
-      </c>
-      <c r="S29" s="61" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="30" spans="6:19" x14ac:dyDescent="0.3">
       <c r="F30" s="43" t="s">
+        <v>342</v>
+      </c>
+      <c r="N30" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="N30" s="1" t="s">
+      <c r="R30" s="61" t="s">
         <v>344</v>
       </c>
-      <c r="R30" s="61" t="s">
+      <c r="S30" s="61" t="s">
         <v>345</v>
-      </c>
-      <c r="S30" s="61" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="31" spans="6:19" x14ac:dyDescent="0.3">
       <c r="N31" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="R31" s="61" t="s">
         <v>347</v>
       </c>
-      <c r="R31" s="61" t="s">
+      <c r="S31" s="61" t="s">
         <v>348</v>
-      </c>
-      <c r="S31" s="61" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="32" spans="6:19" x14ac:dyDescent="0.3">
       <c r="N32" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="R32" s="61" t="s">
         <v>350</v>
       </c>
-      <c r="R32" s="61" t="s">
+      <c r="S32" s="61" t="s">
         <v>351</v>
-      </c>
-      <c r="S32" s="61" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="33" spans="14:19" x14ac:dyDescent="0.3">
@@ -25474,538 +28960,538 @@
         <v>86</v>
       </c>
       <c r="R33" s="61" t="s">
+        <v>352</v>
+      </c>
+      <c r="S33" s="61" t="s">
         <v>353</v>
-      </c>
-      <c r="S33" s="61" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="34" spans="14:19" x14ac:dyDescent="0.3">
       <c r="R34" s="61" t="s">
+        <v>354</v>
+      </c>
+      <c r="S34" s="61" t="s">
         <v>355</v>
-      </c>
-      <c r="S34" s="61" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="35" spans="14:19" x14ac:dyDescent="0.3">
       <c r="R35" s="61" t="s">
+        <v>356</v>
+      </c>
+      <c r="S35" s="61" t="s">
         <v>357</v>
-      </c>
-      <c r="S35" s="61" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="36" spans="14:19" x14ac:dyDescent="0.3">
       <c r="R36" s="61" t="s">
+        <v>358</v>
+      </c>
+      <c r="S36" s="61" t="s">
         <v>359</v>
-      </c>
-      <c r="S36" s="61" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="37" spans="14:19" x14ac:dyDescent="0.3">
       <c r="R37" s="50" t="s">
+        <v>360</v>
+      </c>
+      <c r="S37" s="50" t="s">
         <v>361</v>
-      </c>
-      <c r="S37" s="50" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="38" spans="14:19" x14ac:dyDescent="0.3">
       <c r="R38" s="50" t="s">
+        <v>362</v>
+      </c>
+      <c r="S38" s="50" t="s">
         <v>363</v>
-      </c>
-      <c r="S38" s="50" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="39" spans="14:19" x14ac:dyDescent="0.3">
       <c r="R39" s="50" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="S39" s="50" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="40" spans="14:19" x14ac:dyDescent="0.3">
       <c r="R40" s="61" t="s">
+        <v>365</v>
+      </c>
+      <c r="S40" s="61" t="s">
         <v>366</v>
-      </c>
-      <c r="S40" s="61" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="41" spans="14:19" x14ac:dyDescent="0.3">
       <c r="R41" s="61" t="s">
+        <v>367</v>
+      </c>
+      <c r="S41" s="61" t="s">
         <v>368</v>
-      </c>
-      <c r="S41" s="61" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="42" spans="14:19" x14ac:dyDescent="0.3">
       <c r="R42" s="50" t="s">
+        <v>369</v>
+      </c>
+      <c r="S42" s="50" t="s">
         <v>370</v>
-      </c>
-      <c r="S42" s="50" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="43" spans="14:19" x14ac:dyDescent="0.3">
       <c r="R43" s="50" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="S43" s="50" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="44" spans="14:19" x14ac:dyDescent="0.3">
       <c r="R44" s="61" t="s">
+        <v>372</v>
+      </c>
+      <c r="S44" s="56" t="s">
         <v>373</v>
-      </c>
-      <c r="S44" s="56" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="45" spans="14:19" x14ac:dyDescent="0.3">
       <c r="R45" s="50" t="s">
+        <v>374</v>
+      </c>
+      <c r="S45" s="50" t="s">
         <v>375</v>
-      </c>
-      <c r="S45" s="50" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="46" spans="14:19" x14ac:dyDescent="0.3">
       <c r="R46" s="61" t="s">
+        <v>376</v>
+      </c>
+      <c r="S46" s="61" t="s">
         <v>377</v>
-      </c>
-      <c r="S46" s="61" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="47" spans="14:19" x14ac:dyDescent="0.3">
       <c r="R47" s="50" t="s">
+        <v>378</v>
+      </c>
+      <c r="S47" s="50" t="s">
         <v>379</v>
-      </c>
-      <c r="S47" s="50" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="48" spans="14:19" x14ac:dyDescent="0.3">
       <c r="R48" s="61" t="s">
+        <v>380</v>
+      </c>
+      <c r="S48" s="61" t="s">
         <v>381</v>
-      </c>
-      <c r="S48" s="61" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="49" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R49" s="61" t="s">
+        <v>382</v>
+      </c>
+      <c r="S49" s="61" t="s">
         <v>383</v>
-      </c>
-      <c r="S49" s="61" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="50" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R50" s="61" t="s">
+        <v>384</v>
+      </c>
+      <c r="S50" s="61" t="s">
         <v>385</v>
-      </c>
-      <c r="S50" s="61" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="51" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R51" s="61" t="s">
+        <v>386</v>
+      </c>
+      <c r="S51" s="61" t="s">
         <v>387</v>
-      </c>
-      <c r="S51" s="61" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="52" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R52" s="61" t="s">
+        <v>388</v>
+      </c>
+      <c r="S52" s="61" t="s">
         <v>389</v>
-      </c>
-      <c r="S52" s="61" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="53" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R53" s="61" t="s">
+        <v>390</v>
+      </c>
+      <c r="S53" s="56" t="s">
         <v>391</v>
-      </c>
-      <c r="S53" s="56" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="54" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R54" s="61" t="s">
+        <v>392</v>
+      </c>
+      <c r="S54" s="61" t="s">
         <v>393</v>
-      </c>
-      <c r="S54" s="61" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="55" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R55" s="61" t="s">
+        <v>394</v>
+      </c>
+      <c r="S55" s="61" t="s">
         <v>395</v>
-      </c>
-      <c r="S55" s="61" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="56" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R56" s="61" t="s">
+        <v>396</v>
+      </c>
+      <c r="S56" s="61" t="s">
         <v>397</v>
-      </c>
-      <c r="S56" s="61" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="57" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R57" s="61" t="s">
+        <v>398</v>
+      </c>
+      <c r="S57" s="61" t="s">
         <v>399</v>
-      </c>
-      <c r="S57" s="61" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="58" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R58" s="61" t="s">
+        <v>400</v>
+      </c>
+      <c r="S58" s="61" t="s">
         <v>401</v>
-      </c>
-      <c r="S58" s="61" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="59" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R59" s="61" t="s">
+        <v>402</v>
+      </c>
+      <c r="S59" s="61" t="s">
         <v>403</v>
-      </c>
-      <c r="S59" s="61" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="60" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R60" s="61" t="s">
+        <v>404</v>
+      </c>
+      <c r="S60" s="61" t="s">
         <v>405</v>
-      </c>
-      <c r="S60" s="61" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="61" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R61" s="61" t="s">
+        <v>406</v>
+      </c>
+      <c r="S61" s="61" t="s">
         <v>407</v>
-      </c>
-      <c r="S61" s="61" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="62" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R62" s="61" t="s">
+        <v>408</v>
+      </c>
+      <c r="S62" s="61" t="s">
         <v>409</v>
-      </c>
-      <c r="S62" s="61" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="63" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R63" s="61" t="s">
+        <v>410</v>
+      </c>
+      <c r="S63" s="61" t="s">
         <v>411</v>
-      </c>
-      <c r="S63" s="61" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="64" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R64" s="61" t="s">
+        <v>412</v>
+      </c>
+      <c r="S64" s="61" t="s">
         <v>413</v>
-      </c>
-      <c r="S64" s="61" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="65" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R65" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="S65" s="61" t="s">
         <v>415</v>
-      </c>
-      <c r="S65" s="61" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="66" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R66" s="61" t="s">
+        <v>416</v>
+      </c>
+      <c r="S66" s="61" t="s">
         <v>417</v>
-      </c>
-      <c r="S66" s="61" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="67" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R67" s="61" t="s">
+        <v>418</v>
+      </c>
+      <c r="S67" s="61" t="s">
         <v>419</v>
-      </c>
-      <c r="S67" s="61" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="68" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R68" s="61" t="s">
+        <v>420</v>
+      </c>
+      <c r="S68" s="61" t="s">
         <v>421</v>
-      </c>
-      <c r="S68" s="61" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="69" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R69" s="61" t="s">
+        <v>422</v>
+      </c>
+      <c r="S69" s="61" t="s">
         <v>423</v>
-      </c>
-      <c r="S69" s="61" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="70" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R70" s="61" t="s">
+        <v>424</v>
+      </c>
+      <c r="S70" s="61" t="s">
         <v>425</v>
-      </c>
-      <c r="S70" s="61" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="71" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R71" s="61" t="s">
+        <v>426</v>
+      </c>
+      <c r="S71" s="61" t="s">
         <v>427</v>
-      </c>
-      <c r="S71" s="61" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="72" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R72" s="61" t="s">
+        <v>428</v>
+      </c>
+      <c r="S72" s="1" t="s">
         <v>429</v>
-      </c>
-      <c r="S72" s="1" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="73" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R73" s="50" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="S73" s="50" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="74" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R74" s="61" t="s">
+        <v>431</v>
+      </c>
+      <c r="S74" s="61" t="s">
         <v>432</v>
-      </c>
-      <c r="S74" s="61" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="75" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R75" s="50" t="s">
+        <v>433</v>
+      </c>
+      <c r="S75" s="50" t="s">
         <v>434</v>
-      </c>
-      <c r="S75" s="50" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="76" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R76" s="61" t="s">
+        <v>435</v>
+      </c>
+      <c r="S76" s="61" t="s">
         <v>436</v>
-      </c>
-      <c r="S76" s="61" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="77" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R77" s="61" t="s">
+        <v>437</v>
+      </c>
+      <c r="S77" s="61" t="s">
         <v>438</v>
-      </c>
-      <c r="S77" s="61" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="78" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R78" s="50" t="s">
+        <v>439</v>
+      </c>
+      <c r="S78" s="50" t="s">
         <v>440</v>
-      </c>
-      <c r="S78" s="50" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="79" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R79" s="50" t="s">
+        <v>441</v>
+      </c>
+      <c r="S79" s="50" t="s">
         <v>442</v>
-      </c>
-      <c r="S79" s="50" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="80" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R80" s="61" t="s">
+        <v>443</v>
+      </c>
+      <c r="S80" s="61" t="s">
         <v>444</v>
-      </c>
-      <c r="S80" s="61" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="81" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R81" s="61" t="s">
+        <v>445</v>
+      </c>
+      <c r="S81" s="61" t="s">
         <v>446</v>
-      </c>
-      <c r="S81" s="61" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="82" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R82" s="61" t="s">
+        <v>447</v>
+      </c>
+      <c r="S82" s="61" t="s">
         <v>448</v>
-      </c>
-      <c r="S82" s="61" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="83" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R83" s="50" t="s">
+        <v>449</v>
+      </c>
+      <c r="S83" s="50" t="s">
         <v>450</v>
-      </c>
-      <c r="S83" s="50" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="84" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R84" s="50" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="S84" s="50" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="85" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R85" s="61" t="s">
+        <v>452</v>
+      </c>
+      <c r="S85" s="61" t="s">
         <v>453</v>
-      </c>
-      <c r="S85" s="61" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="86" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R86" s="61" t="s">
+        <v>454</v>
+      </c>
+      <c r="S86" s="61" t="s">
         <v>455</v>
-      </c>
-      <c r="S86" s="61" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="87" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R87" s="61" t="s">
+        <v>456</v>
+      </c>
+      <c r="S87" s="61" t="s">
         <v>457</v>
-      </c>
-      <c r="S87" s="61" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="88" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R88" s="61" t="s">
+        <v>458</v>
+      </c>
+      <c r="S88" s="61" t="s">
         <v>459</v>
-      </c>
-      <c r="S88" s="61" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="89" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R89" s="61" t="s">
+        <v>460</v>
+      </c>
+      <c r="S89" s="61" t="s">
         <v>461</v>
-      </c>
-      <c r="S89" s="61" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="90" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R90" s="61" t="s">
+        <v>462</v>
+      </c>
+      <c r="S90" s="61" t="s">
         <v>463</v>
-      </c>
-      <c r="S90" s="61" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="91" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R91" s="61" t="s">
+        <v>464</v>
+      </c>
+      <c r="S91" s="61" t="s">
         <v>465</v>
-      </c>
-      <c r="S91" s="61" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="92" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R92" s="61" t="s">
+        <v>466</v>
+      </c>
+      <c r="S92" s="61" t="s">
         <v>467</v>
-      </c>
-      <c r="S92" s="61" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="93" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R93" s="61" t="s">
+        <v>468</v>
+      </c>
+      <c r="S93" s="1" t="s">
         <v>469</v>
-      </c>
-      <c r="S93" s="1" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="94" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R94" s="61" t="s">
+        <v>470</v>
+      </c>
+      <c r="S94" s="61" t="s">
         <v>471</v>
-      </c>
-      <c r="S94" s="61" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="95" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R95" s="61" t="s">
+        <v>472</v>
+      </c>
+      <c r="S95" s="61" t="s">
         <v>473</v>
-      </c>
-      <c r="S95" s="61" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="96" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R96" s="61" t="s">
+        <v>474</v>
+      </c>
+      <c r="S96" s="1" t="s">
         <v>475</v>
-      </c>
-      <c r="S96" s="1" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="97" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R97" s="61" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="S97" s="35" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="98" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R98" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="S98" s="35" t="s">
         <v>478</v>
-      </c>
-      <c r="S98" s="35" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="99" spans="18:19" x14ac:dyDescent="0.3">
       <c r="R99" s="61" t="s">
+        <v>479</v>
+      </c>
+      <c r="S99" s="1" t="s">
         <v>480</v>
-      </c>
-      <c r="S99" s="1" t="s">
-        <v>481</v>
       </c>
     </row>
   </sheetData>
